--- a/Raw/SDMR_FIELD.xlsx
+++ b/Raw/SDMR_FIELD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katia\Desktop\STAGE\M1\Travail\Stage_M1_UWS\Raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mnhnfr.sharepoint.com/sites/ParisWildness/Documents partages/General/Data/Vegetation data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{618FF378-8832-4BF1-A65C-9BE3A0521984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D7609B0-7474-441A-99CB-6AD4A8300BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="transect" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
     <t>Autres</t>
   </si>
   <si>
-    <t>19E_32</t>
+    <t>19E_33</t>
   </si>
   <si>
     <t>/</t>
@@ -252,6 +252,87 @@
     <t>Certains endroits avec du bitume en état moyen</t>
   </si>
   <si>
+    <t>7E_19</t>
+  </si>
+  <si>
+    <t>11-11bis rue Casimir Perier</t>
+  </si>
+  <si>
+    <t>7E_7</t>
+  </si>
+  <si>
+    <t>Rue de Varenne</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>7E_11</t>
+  </si>
+  <si>
+    <t>2 rue Oudinot</t>
+  </si>
+  <si>
+    <t>7E_9</t>
+  </si>
+  <si>
+    <t>Avenue de Breteuil</t>
+  </si>
+  <si>
+    <t>L'habitat "chemin" est lelong de la transition avec l'espace vert</t>
+  </si>
+  <si>
+    <t>7E_8</t>
+  </si>
+  <si>
+    <t>Pavés, bitume, gravier/sol</t>
+  </si>
+  <si>
+    <t>7E_27</t>
+  </si>
+  <si>
+    <t>Rue du général Lambert</t>
+  </si>
+  <si>
+    <t>Transition à espace vert au bout du transect ; Autre habitat : bac</t>
+  </si>
+  <si>
+    <t>Mur, grillage, Transition à espace vert</t>
+  </si>
+  <si>
+    <t>7E_26</t>
+  </si>
+  <si>
+    <t>Transect entre pelouse et route ; Autre habitat : bord du côté pelouse, entre le petit grillage et le trottoir</t>
+  </si>
+  <si>
+    <t>Grillage, transition avec espace vert</t>
+  </si>
+  <si>
+    <t>7E_5</t>
+  </si>
+  <si>
+    <t>Sorte de terr-plein piéton, séparant 2 routes ; petite partie de gravier/sol autour d'arbre/grand pied d'arbre donc mis dans pied d'arbre</t>
+  </si>
+  <si>
+    <t>Route (vélo et parking)</t>
+  </si>
+  <si>
+    <t>7E_25</t>
+  </si>
+  <si>
+    <t>A nouveau terre-plein entre 2 routes, mais piéton et avec bancs ! Habitats : pied d'arbre isolé car un cerle en métal les délimite, et un chemin les relie</t>
+  </si>
+  <si>
+    <t>Buf</t>
+  </si>
+  <si>
+    <t>15bis rue Buffon</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
     <t>Horticole</t>
   </si>
   <si>
@@ -591,48 +672,12 @@
     <t>Geranium robertianum</t>
   </si>
   <si>
-    <t>7E_19</t>
-  </si>
-  <si>
     <t>Plantule crepis ?</t>
   </si>
   <si>
-    <t>7E_7</t>
-  </si>
-  <si>
-    <t>11-11bis rue Casimir Perier</t>
-  </si>
-  <si>
-    <t>Rue de Varenne</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>7E_11</t>
-  </si>
-  <si>
-    <t>2 rue Oudinot</t>
-  </si>
-  <si>
-    <t>7E_9</t>
-  </si>
-  <si>
-    <t>Avenue de Breteuil</t>
-  </si>
-  <si>
-    <t>L'habitat "chemin" est lelong de la transition avec l'espace vert</t>
-  </si>
-  <si>
     <t>Brassicaceae sp</t>
   </si>
   <si>
-    <t>7E_8</t>
-  </si>
-  <si>
-    <t>Pavés, bitume, gravier/sol</t>
-  </si>
-  <si>
     <t>Cirsium sp</t>
   </si>
   <si>
@@ -645,18 +690,6 @@
     <t>Duchesnea indica</t>
   </si>
   <si>
-    <t>7E_27</t>
-  </si>
-  <si>
-    <t>Rue du général Lambert</t>
-  </si>
-  <si>
-    <t>Mur, grillage, Transition à espace vert</t>
-  </si>
-  <si>
-    <t>Transition à espace vert au bout du transect ; Autre habitat : bac</t>
-  </si>
-  <si>
     <t>horticole 1</t>
   </si>
   <si>
@@ -681,15 +714,6 @@
     <t>Senecio vulgaris</t>
   </si>
   <si>
-    <t>7E_26</t>
-  </si>
-  <si>
-    <t>Transect entre pelouse et route ; Autre habitat : bord du côté pelouse, entre le petit grillage et le trottoir</t>
-  </si>
-  <si>
-    <t>Grillage, transition avec espace vert</t>
-  </si>
-  <si>
     <t>Prunella vulgaris</t>
   </si>
   <si>
@@ -700,30 +724,6 @@
   </si>
   <si>
     <t>Torilis nodosa</t>
-  </si>
-  <si>
-    <t>7E_5</t>
-  </si>
-  <si>
-    <t>7E_25</t>
-  </si>
-  <si>
-    <t>Route (vélo et parking)</t>
-  </si>
-  <si>
-    <t>Sorte de terr-plein piéton, séparant 2 routes ; petite partie de gravier/sol autour d'arbre/grand pied d'arbre donc mis dans pied d'arbre</t>
-  </si>
-  <si>
-    <t>A nouveau terre-plein entre 2 routes, mais piéton et avec bancs ! Habitats : pied d'arbre isolé car un cerle en métal les délimite, et un chemin les relie</t>
-  </si>
-  <si>
-    <t>Buf</t>
-  </si>
-  <si>
-    <t>15bis rue Buffon</t>
-  </si>
-  <si>
-    <t>Test</t>
   </si>
   <si>
     <t>Plantule dicot</t>
@@ -760,7 +760,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -822,14 +822,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -867,7 +863,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -973,7 +969,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1115,7 +1111,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1124,24 +1120,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23">
       <c r="A1" s="3"/>
       <c r="F1" s="4" t="s">
         <v>0</v>
@@ -1161,7 +1157,7 @@
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1232,7 +1228,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="28.9">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -1279,7 +1275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23">
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
@@ -1329,7 +1325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -1376,7 +1372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" ht="43.15">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -1429,7 +1425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -1482,7 +1478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23">
       <c r="A8" s="3" t="s">
         <v>47</v>
       </c>
@@ -1529,7 +1525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23">
       <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
@@ -1576,7 +1572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23">
       <c r="A10" s="3" t="s">
         <v>53</v>
       </c>
@@ -1626,7 +1622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23">
       <c r="A11" s="3" t="s">
         <v>55</v>
       </c>
@@ -1679,7 +1675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23">
       <c r="A12" s="3" t="s">
         <v>61</v>
       </c>
@@ -1726,7 +1722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -1773,7 +1769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="43.15">
       <c r="A14" t="s">
         <v>64</v>
       </c>
@@ -1814,7 +1810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" ht="28.9">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -1867,12 +1863,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23">
       <c r="A16" t="s">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1">
         <v>46128</v>
@@ -1914,12 +1910,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23">
       <c r="A17" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="C17" s="1">
         <v>46128</v>
@@ -1958,15 +1954,15 @@
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" t="s">
-        <v>190</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="C18" s="1">
         <v>46128</v>
@@ -2008,12 +2004,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" ht="28.9">
       <c r="A19" t="s">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="C19" s="1">
         <v>46128</v>
@@ -2022,7 +2018,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="F19">
         <v>13</v>
@@ -2058,9 +2054,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23">
       <c r="A20" t="s">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="C20" s="1">
         <v>46128</v>
@@ -2075,7 +2071,7 @@
         <v>48</v>
       </c>
       <c r="J20" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s">
         <v>31</v>
@@ -2102,12 +2098,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" ht="28.9">
       <c r="A21" t="s">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="C21" s="1">
         <v>46129</v>
@@ -2116,7 +2112,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>205</v>
+        <v>85</v>
       </c>
       <c r="F21">
         <v>3</v>
@@ -2131,13 +2127,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s">
         <v>31</v>
       </c>
       <c r="L21" t="s">
-        <v>204</v>
+        <v>86</v>
       </c>
       <c r="M21">
         <v>1</v>
@@ -2158,9 +2154,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" ht="43.15">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>87</v>
       </c>
       <c r="C22" s="1">
         <v>46129</v>
@@ -2169,7 +2165,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>215</v>
+        <v>88</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -2190,7 +2186,7 @@
         <v>31</v>
       </c>
       <c r="L22" t="s">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c r="M22">
         <v>1</v>
@@ -2205,9 +2201,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" ht="57.6">
       <c r="A23" t="s">
-        <v>221</v>
+        <v>90</v>
       </c>
       <c r="B23">
         <v>18</v>
@@ -2219,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -2234,13 +2230,13 @@
         <v>34</v>
       </c>
       <c r="J23" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s">
         <v>31</v>
       </c>
       <c r="L23" t="s">
-        <v>223</v>
+        <v>92</v>
       </c>
       <c r="M23">
         <v>1</v>
@@ -2252,9 +2248,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" ht="72">
       <c r="A24" t="s">
-        <v>222</v>
+        <v>93</v>
       </c>
       <c r="B24">
         <v>12</v>
@@ -2266,7 +2262,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>225</v>
+        <v>94</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -2281,13 +2277,13 @@
         <v>34</v>
       </c>
       <c r="J24" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s">
         <v>31</v>
       </c>
       <c r="L24" t="s">
-        <v>223</v>
+        <v>92</v>
       </c>
       <c r="M24">
         <v>1</v>
@@ -2302,12 +2298,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23">
       <c r="A25" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>227</v>
+        <v>96</v>
       </c>
       <c r="C25" s="1">
         <v>46125</v>
@@ -2316,7 +2312,7 @@
         <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="F25">
         <v>9</v>
@@ -2370,64 +2366,64 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B3963A-ED2B-41F3-80D1-989660668753}">
   <dimension ref="A1:N334"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="F1" t="s">
         <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="H1" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="I1" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="J1" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="K1" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="L1" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="M1" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="N1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
@@ -2435,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -2471,7 +2467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -2479,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -2515,7 +2511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -2523,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -2559,7 +2555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -2567,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -2603,15 +2599,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14">
       <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -2647,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14">
       <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
@@ -2655,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -2691,7 +2687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14">
       <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
@@ -2699,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2735,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14">
       <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
@@ -2743,13 +2739,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14">
       <c r="A10" s="3" t="s">
         <v>25</v>
       </c>
@@ -2757,68 +2753,68 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="L10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="L11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="L12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14">
       <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14">
       <c r="A15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="L15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -2826,184 +2822,184 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="L16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12">
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12">
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12">
       <c r="A19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="L19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12">
       <c r="A20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12">
       <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12">
       <c r="A22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12">
       <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12">
       <c r="A24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="L24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12">
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12">
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12">
       <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="L27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12">
       <c r="A28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="L28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12">
       <c r="A29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12">
       <c r="A30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="L30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12">
       <c r="A31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="L31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12">
       <c r="A32" s="3" t="s">
         <v>25</v>
       </c>
@@ -3011,40 +3007,40 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="L32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12">
       <c r="A33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12">
       <c r="A34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12">
       <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -3059,23 +3055,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12">
       <c r="A36" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12">
       <c r="A37" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -3087,12 +3083,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12">
       <c r="A38" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3104,12 +3100,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12">
       <c r="A39" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -3121,45 +3117,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12">
       <c r="A40" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12">
       <c r="A41" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12">
       <c r="A42" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C42" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12">
       <c r="A43" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -3168,23 +3164,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12">
       <c r="A44" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12">
       <c r="A45" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C45" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -3193,56 +3189,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12">
       <c r="A46" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12">
       <c r="A47" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C47" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12">
       <c r="A48" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C48" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8">
       <c r="A49" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C49" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8">
       <c r="A50" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -3251,34 +3247,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8">
       <c r="A51" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8">
       <c r="A52" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C52" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8">
       <c r="A53" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3287,23 +3283,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8">
       <c r="A54" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C54" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8">
       <c r="A55" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -3312,12 +3308,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8">
       <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C56" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3326,23 +3322,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8">
       <c r="A57" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8">
       <c r="A58" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C58" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -3351,12 +3347,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8">
       <c r="A59" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -3365,23 +3361,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8">
       <c r="A60" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8">
       <c r="A61" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C61" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3390,23 +3386,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8">
       <c r="A62" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C62" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8">
       <c r="A63" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3415,34 +3411,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8">
       <c r="A64" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11">
       <c r="A65" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C65" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="G65">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11">
       <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3451,56 +3447,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11">
       <c r="A67" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C67" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11">
       <c r="A68" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C68" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11">
       <c r="A69" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C69" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11">
       <c r="A70" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C70" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="D70">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11">
       <c r="A71" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C71" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -3509,7 +3505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11">
       <c r="A72" s="3" t="s">
         <v>40</v>
       </c>
@@ -3517,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -3526,7 +3522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11">
       <c r="A73" s="3" t="s">
         <v>40</v>
       </c>
@@ -3534,27 +3530,27 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="K73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11">
       <c r="A74" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C74" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="K74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11">
       <c r="A75" s="3" t="s">
         <v>40</v>
       </c>
@@ -3562,13 +3558,13 @@
         <v>1</v>
       </c>
       <c r="C75" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="K75">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11">
       <c r="A76" s="3" t="s">
         <v>40</v>
       </c>
@@ -3576,13 +3572,13 @@
         <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11">
       <c r="A77" s="3" t="s">
         <v>40</v>
       </c>
@@ -3590,13 +3586,13 @@
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="K77">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11">
       <c r="A78" s="3" t="s">
         <v>40</v>
       </c>
@@ -3604,13 +3600,13 @@
         <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="K78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11">
       <c r="A79" s="3" t="s">
         <v>40</v>
       </c>
@@ -3618,32 +3614,32 @@
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="K79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11">
       <c r="A80" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C80" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="K80">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8">
       <c r="A81" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3652,12 +3648,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8">
       <c r="A82" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C82" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3666,100 +3662,100 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8">
       <c r="A83" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C83" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G83">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8">
       <c r="A84" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C84" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8">
       <c r="A85" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C85" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E85">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8">
       <c r="A86" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C86" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8">
       <c r="A87" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="G87">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8">
       <c r="A88" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C88" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8">
       <c r="A89" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C89" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8">
       <c r="A90" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C90" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8">
       <c r="A91" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C91" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -3768,12 +3764,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8">
       <c r="A92" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C92" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -3782,34 +3778,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8">
       <c r="A93" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C93" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G93">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8">
       <c r="A94" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C94" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G94">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8">
       <c r="A95" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C95" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -3818,45 +3814,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8">
       <c r="A96" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C96" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14">
       <c r="A97" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C97" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="G97">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14">
       <c r="A98" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C98" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="G98">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14">
       <c r="A99" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C99" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -3865,12 +3861,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14">
       <c r="A100" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C100" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -3879,23 +3875,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14">
       <c r="A101" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C101" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="G101">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14">
       <c r="A102" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C102" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -3904,45 +3900,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14">
       <c r="A103" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C103" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="G103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14">
       <c r="A104" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C104" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="G104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14">
       <c r="A105" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C105" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="G105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14">
       <c r="A106" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C106" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -3951,12 +3947,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14">
       <c r="A107" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C107" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -3965,12 +3961,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14">
       <c r="A108" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C108" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -3979,29 +3975,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14">
       <c r="A109" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C109" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="N109">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14">
       <c r="A110" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C110" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="N110">
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14">
       <c r="A111" s="3" t="s">
         <v>50</v>
       </c>
@@ -4009,32 +4005,32 @@
         <v>1</v>
       </c>
       <c r="C111" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="N111">
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14">
       <c r="A112" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C112" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="N112">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14">
       <c r="A113" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B113" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C113" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -4046,12 +4042,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14">
       <c r="A114" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C114" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -4060,34 +4056,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14">
       <c r="A115" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C115" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="H115">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14">
       <c r="A116" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C116" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="H116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14">
       <c r="A117" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C117" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -4096,12 +4092,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14">
       <c r="A118" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C118" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -4110,111 +4106,111 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14">
       <c r="A119" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C119" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G119">
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14">
       <c r="A120" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C120" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G120">
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14">
       <c r="A121" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C121" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="G121">
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14">
       <c r="A122" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C122" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G122">
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14">
       <c r="A123" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C123" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G123">
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14">
       <c r="A124" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C124" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="H124">
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14">
       <c r="A125" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C125" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="H125">
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14">
       <c r="A126" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C126" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="H126">
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14">
       <c r="A127" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C127" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="G127">
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14">
       <c r="A128" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C128" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4226,23 +4222,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13">
       <c r="A129" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C129" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13">
       <c r="A130" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C130" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4254,34 +4250,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13">
       <c r="A131" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C131" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="G131">
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13">
       <c r="A132" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C132" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G132">
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13">
       <c r="A133" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C133" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -4290,45 +4286,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13">
       <c r="A134" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C134" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="G134">
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13">
       <c r="A135" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C135" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="H135">
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13">
       <c r="A136" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C136" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="H136">
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13">
       <c r="A137" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C137" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -4337,34 +4333,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13">
       <c r="A138" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C138" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="H138">
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13">
       <c r="A139" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C139" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="H139">
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13">
       <c r="A140" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C140" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -4376,23 +4372,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13">
       <c r="A141" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C141" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G141">
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13">
       <c r="A142" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C142" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -4404,12 +4400,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13">
       <c r="A143" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C143" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -4418,12 +4414,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13">
       <c r="A144" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C144" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -4435,34 +4431,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13">
       <c r="A145" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C145" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G145">
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13">
       <c r="A146" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C146" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="M146">
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13">
       <c r="A147" t="s">
         <v>61</v>
       </c>
       <c r="C147" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -4471,73 +4467,73 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13">
       <c r="A148" t="s">
         <v>61</v>
       </c>
       <c r="C148" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G148">
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13">
       <c r="A149" t="s">
         <v>61</v>
       </c>
       <c r="C149" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="G149">
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13">
       <c r="A150" t="s">
         <v>61</v>
       </c>
       <c r="C150" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="G150">
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13">
       <c r="A151" t="s">
         <v>61</v>
       </c>
       <c r="C151" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="G151">
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13">
       <c r="A152" t="s">
         <v>61</v>
       </c>
       <c r="C152" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="G152">
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13">
       <c r="A153" t="s">
         <v>61</v>
       </c>
       <c r="C153" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="G153">
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13">
       <c r="A154" t="s">
         <v>61</v>
       </c>
@@ -4545,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="C154" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -4554,23 +4550,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13">
       <c r="A155" t="s">
         <v>63</v>
       </c>
       <c r="C155" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="G155">
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13">
       <c r="A156" t="s">
         <v>63</v>
       </c>
       <c r="C156" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -4582,111 +4578,111 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13">
       <c r="A157" t="s">
         <v>63</v>
       </c>
       <c r="C157" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="H157">
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13">
       <c r="A158" t="s">
         <v>63</v>
       </c>
       <c r="C158" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="H158">
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13">
       <c r="A159" t="s">
         <v>63</v>
       </c>
       <c r="C159" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="H159">
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13">
       <c r="A160" t="s">
         <v>63</v>
       </c>
       <c r="C160" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="H160">
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8">
       <c r="A161" t="s">
         <v>63</v>
       </c>
       <c r="C161" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8">
       <c r="A162" t="s">
         <v>63</v>
       </c>
       <c r="C162" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="H162">
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8">
       <c r="A163" t="s">
         <v>63</v>
       </c>
       <c r="C163" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="H163">
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8">
       <c r="A164" t="s">
         <v>63</v>
       </c>
       <c r="C164" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="G164">
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8">
       <c r="A165" t="s">
         <v>63</v>
       </c>
       <c r="C165" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G165">
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8">
       <c r="A166" t="s">
         <v>64</v>
       </c>
       <c r="C166" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="E166">
         <v>1</v>
@@ -4695,12 +4691,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8">
       <c r="A167" t="s">
         <v>64</v>
       </c>
       <c r="C167" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -4709,23 +4705,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8">
       <c r="A168" t="s">
         <v>64</v>
       </c>
       <c r="C168" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G168">
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8">
       <c r="A169" t="s">
         <v>64</v>
       </c>
       <c r="C169" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="E169">
         <v>1</v>
@@ -4734,56 +4730,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8">
       <c r="A170" t="s">
         <v>64</v>
       </c>
       <c r="C170" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="G170">
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8">
       <c r="A171" t="s">
         <v>64</v>
       </c>
       <c r="C171" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="G171">
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8">
       <c r="A172" t="s">
         <v>64</v>
       </c>
       <c r="C172" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G172">
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8">
       <c r="A173" t="s">
         <v>64</v>
       </c>
       <c r="C173" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="G173">
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8">
       <c r="A174" t="s">
         <v>64</v>
       </c>
       <c r="C174" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="E174">
         <v>1</v>
@@ -4792,12 +4788,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8">
       <c r="A175" t="s">
         <v>64</v>
       </c>
       <c r="C175" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="E175">
         <v>1</v>
@@ -4806,12 +4802,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8">
       <c r="A176" t="s">
         <v>64</v>
       </c>
       <c r="C176" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="E176">
         <v>1</v>
@@ -4820,78 +4816,78 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9">
       <c r="A177" t="s">
         <v>64</v>
       </c>
       <c r="C177" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G177">
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9">
       <c r="A178" t="s">
         <v>64</v>
       </c>
       <c r="C178" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="G178">
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9">
       <c r="A179" t="s">
         <v>64</v>
       </c>
       <c r="C179" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="G179">
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9">
       <c r="A180" t="s">
         <v>64</v>
       </c>
       <c r="C180" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="G180">
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9">
       <c r="A181" t="s">
         <v>64</v>
       </c>
       <c r="C181" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="E181">
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9">
       <c r="A182" t="s">
         <v>68</v>
       </c>
       <c r="C182" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="I182">
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9">
       <c r="A183" t="s">
         <v>68</v>
       </c>
       <c r="C183" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -4903,12 +4899,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9">
       <c r="A184" t="s">
         <v>68</v>
       </c>
       <c r="C184" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -4917,34 +4913,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9">
       <c r="A185" t="s">
         <v>68</v>
       </c>
       <c r="C185" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="I185">
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9">
       <c r="A186" t="s">
         <v>68</v>
       </c>
       <c r="C186" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G186">
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9">
       <c r="A187" t="s">
         <v>68</v>
       </c>
       <c r="C187" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E187">
         <v>1</v>
@@ -4953,12 +4949,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9">
       <c r="A188" t="s">
         <v>68</v>
       </c>
       <c r="C188" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -4967,34 +4963,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9">
       <c r="A189" t="s">
         <v>68</v>
       </c>
       <c r="C189" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="I189">
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9">
       <c r="A190" t="s">
         <v>68</v>
       </c>
       <c r="C190" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="I190">
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9">
       <c r="A191" t="s">
         <v>68</v>
       </c>
       <c r="C191" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -5006,34 +5002,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9">
       <c r="A192" t="s">
         <v>68</v>
       </c>
       <c r="C192" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G192">
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9">
       <c r="A193" t="s">
         <v>68</v>
       </c>
       <c r="C193" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="G193">
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9">
       <c r="A194" t="s">
         <v>68</v>
       </c>
       <c r="C194" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="G194">
         <v>1</v>
@@ -5042,1450 +5038,1450 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9">
       <c r="A195" t="s">
         <v>68</v>
       </c>
       <c r="C195" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="I195">
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9">
       <c r="A196" t="s">
         <v>68</v>
       </c>
       <c r="C196" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="I196">
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9">
       <c r="A197" t="s">
         <v>68</v>
       </c>
       <c r="C197" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="I197">
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9">
       <c r="A198" t="s">
         <v>68</v>
       </c>
       <c r="C198" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="I198">
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9">
       <c r="A199" t="s">
         <v>68</v>
       </c>
       <c r="C199" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="G199">
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9">
       <c r="A200" t="s">
         <v>68</v>
       </c>
       <c r="C200" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G200">
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9">
       <c r="A201" t="s">
         <v>68</v>
       </c>
       <c r="C201" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="G201">
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9">
       <c r="A202" t="s">
         <v>68</v>
       </c>
       <c r="C202" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="I202">
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9">
       <c r="A203" t="s">
+        <v>71</v>
+      </c>
+      <c r="C203" t="s">
+        <v>111</v>
+      </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+      <c r="E203">
+        <v>1</v>
+      </c>
+      <c r="G203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" t="s">
+        <v>71</v>
+      </c>
+      <c r="C204" t="s">
+        <v>148</v>
+      </c>
+      <c r="E204">
+        <v>1</v>
+      </c>
+      <c r="G204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" t="s">
+        <v>71</v>
+      </c>
+      <c r="C205" t="s">
+        <v>121</v>
+      </c>
+      <c r="E205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" t="s">
+        <v>71</v>
+      </c>
+      <c r="C206" t="s">
+        <v>141</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206">
+        <v>1</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+      <c r="G206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" t="s">
+        <v>71</v>
+      </c>
+      <c r="C207" t="s">
+        <v>150</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" t="s">
+        <v>71</v>
+      </c>
+      <c r="C208" t="s">
+        <v>211</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13">
+      <c r="A209" t="s">
+        <v>71</v>
+      </c>
+      <c r="C209" t="s">
+        <v>114</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13">
+      <c r="A210" t="s">
+        <v>71</v>
+      </c>
+      <c r="C210" t="s">
+        <v>136</v>
+      </c>
+      <c r="G210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13">
+      <c r="A211" t="s">
+        <v>73</v>
+      </c>
+      <c r="C211" t="s">
+        <v>114</v>
+      </c>
+      <c r="G211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13">
+      <c r="A212" t="s">
+        <v>73</v>
+      </c>
+      <c r="C212" t="s">
+        <v>111</v>
+      </c>
+      <c r="G212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13">
+      <c r="A213" t="s">
+        <v>73</v>
+      </c>
+      <c r="C213" t="s">
+        <v>136</v>
+      </c>
+      <c r="G213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13">
+      <c r="A214" t="s">
+        <v>73</v>
+      </c>
+      <c r="C214" t="s">
+        <v>141</v>
+      </c>
+      <c r="E214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13">
+      <c r="A215" t="s">
+        <v>76</v>
+      </c>
+      <c r="C215" t="s">
+        <v>136</v>
+      </c>
+      <c r="G215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13">
+      <c r="A216" t="s">
+        <v>76</v>
+      </c>
+      <c r="C216" t="s">
+        <v>114</v>
+      </c>
+      <c r="G216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13">
+      <c r="A217" t="s">
+        <v>78</v>
+      </c>
+      <c r="C217" t="s">
+        <v>111</v>
+      </c>
+      <c r="G217">
+        <v>1</v>
+      </c>
+      <c r="H217">
+        <v>1</v>
+      </c>
+      <c r="M217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13">
+      <c r="A218" t="s">
+        <v>78</v>
+      </c>
+      <c r="C218" t="s">
+        <v>201</v>
+      </c>
+      <c r="G218">
+        <v>1</v>
+      </c>
+      <c r="H218">
+        <v>1</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13">
+      <c r="A219" t="s">
+        <v>78</v>
+      </c>
+      <c r="C219" t="s">
+        <v>121</v>
+      </c>
+      <c r="H219">
+        <v>1</v>
+      </c>
+      <c r="M219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13">
+      <c r="A220" t="s">
+        <v>78</v>
+      </c>
+      <c r="C220" t="s">
+        <v>206</v>
+      </c>
+      <c r="H220">
+        <v>1</v>
+      </c>
+      <c r="M220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13">
+      <c r="A221" t="s">
+        <v>78</v>
+      </c>
+      <c r="C221" t="s">
+        <v>152</v>
+      </c>
+      <c r="G221">
+        <v>1</v>
+      </c>
+      <c r="M221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13">
+      <c r="A222" t="s">
+        <v>78</v>
+      </c>
+      <c r="C222" t="s">
+        <v>148</v>
+      </c>
+      <c r="H222">
+        <v>1</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13">
+      <c r="A223" t="s">
+        <v>78</v>
+      </c>
+      <c r="C223" t="s">
+        <v>208</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13">
+      <c r="A224" t="s">
+        <v>78</v>
+      </c>
+      <c r="C224" t="s">
+        <v>172</v>
+      </c>
+      <c r="H224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13">
+      <c r="A225" t="s">
+        <v>78</v>
+      </c>
+      <c r="C225" t="s">
+        <v>114</v>
+      </c>
+      <c r="G225">
+        <v>1</v>
+      </c>
+      <c r="H225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13">
+      <c r="A226" t="s">
+        <v>78</v>
+      </c>
+      <c r="C226" t="s">
+        <v>132</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13">
+      <c r="A227" t="s">
+        <v>78</v>
+      </c>
+      <c r="C227" t="s">
+        <v>153</v>
+      </c>
+      <c r="H227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13">
+      <c r="A228" t="s">
+        <v>78</v>
+      </c>
+      <c r="C228" t="s">
+        <v>147</v>
+      </c>
+      <c r="H228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13">
+      <c r="A229" t="s">
+        <v>78</v>
+      </c>
+      <c r="C229" t="s">
+        <v>157</v>
+      </c>
+      <c r="H229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13">
+      <c r="A230" t="s">
+        <v>78</v>
+      </c>
+      <c r="C230" t="s">
+        <v>150</v>
+      </c>
+      <c r="H230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13">
+      <c r="A231" t="s">
+        <v>78</v>
+      </c>
+      <c r="C231" t="s">
+        <v>212</v>
+      </c>
+      <c r="H231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13">
+      <c r="A232" t="s">
+        <v>78</v>
+      </c>
+      <c r="C232" t="s">
+        <v>154</v>
+      </c>
+      <c r="H232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13">
+      <c r="A233" t="s">
+        <v>78</v>
+      </c>
+      <c r="C233" t="s">
+        <v>136</v>
+      </c>
+      <c r="G233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13">
+      <c r="A234" t="s">
+        <v>81</v>
+      </c>
+      <c r="C234" t="s">
+        <v>121</v>
+      </c>
+      <c r="E234">
+        <v>1</v>
+      </c>
+      <c r="G234">
+        <v>1</v>
+      </c>
+      <c r="H234">
+        <v>1</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13">
+      <c r="A235" t="s">
+        <v>81</v>
+      </c>
+      <c r="C235" t="s">
+        <v>111</v>
+      </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
+      <c r="G235">
+        <v>1</v>
+      </c>
+      <c r="H235">
+        <v>1</v>
+      </c>
+      <c r="M235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13">
+      <c r="A236" t="s">
+        <v>81</v>
+      </c>
+      <c r="C236" t="s">
+        <v>114</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+      <c r="G236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13">
+      <c r="A237" t="s">
+        <v>81</v>
+      </c>
+      <c r="C237" t="s">
+        <v>213</v>
+      </c>
+      <c r="E237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13">
+      <c r="A238" t="s">
+        <v>81</v>
+      </c>
+      <c r="C238" t="s">
+        <v>147</v>
+      </c>
+      <c r="E238">
+        <v>1</v>
+      </c>
+      <c r="G238">
+        <v>1</v>
+      </c>
+      <c r="H238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13">
+      <c r="A239" t="s">
+        <v>81</v>
+      </c>
+      <c r="C239" t="s">
+        <v>136</v>
+      </c>
+      <c r="E239">
+        <v>1</v>
+      </c>
+      <c r="G239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13">
+      <c r="A240" t="s">
+        <v>81</v>
+      </c>
+      <c r="C240" t="s">
+        <v>148</v>
+      </c>
+      <c r="E240">
+        <v>1</v>
+      </c>
+      <c r="G240">
+        <v>1</v>
+      </c>
+      <c r="H240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14">
+      <c r="A241" t="s">
+        <v>81</v>
+      </c>
+      <c r="C241" t="s">
+        <v>117</v>
+      </c>
+      <c r="E241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14">
+      <c r="A242" t="s">
+        <v>81</v>
+      </c>
+      <c r="C242" t="s">
+        <v>209</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14">
+      <c r="A243" t="s">
+        <v>81</v>
+      </c>
+      <c r="C243" t="s">
+        <v>154</v>
+      </c>
+      <c r="E243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14">
+      <c r="A244" t="s">
+        <v>81</v>
+      </c>
+      <c r="C244" t="s">
+        <v>214</v>
+      </c>
+      <c r="E244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14">
+      <c r="A245" t="s">
+        <v>81</v>
+      </c>
+      <c r="C245" t="s">
+        <v>215</v>
+      </c>
+      <c r="E245">
+        <v>1</v>
+      </c>
+      <c r="G245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14">
+      <c r="A246" t="s">
+        <v>81</v>
+      </c>
+      <c r="C246" t="s">
+        <v>216</v>
+      </c>
+      <c r="E246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14">
+      <c r="A247" t="s">
+        <v>81</v>
+      </c>
+      <c r="C247" t="s">
+        <v>150</v>
+      </c>
+      <c r="G247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14">
+      <c r="A248" t="s">
+        <v>81</v>
+      </c>
+      <c r="C248" t="s">
+        <v>175</v>
+      </c>
+      <c r="G248">
+        <v>1</v>
+      </c>
+      <c r="M248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14">
+      <c r="A249" t="s">
+        <v>81</v>
+      </c>
+      <c r="C249" t="s">
+        <v>141</v>
+      </c>
+      <c r="E249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14">
+      <c r="A250" t="s">
+        <v>81</v>
+      </c>
+      <c r="C250" t="s">
         <v>184</v>
       </c>
-      <c r="C203" t="s">
-        <v>84</v>
-      </c>
-      <c r="D203">
-        <v>1</v>
-      </c>
-      <c r="E203">
-        <v>1</v>
-      </c>
-      <c r="G203">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>184</v>
-      </c>
-      <c r="C204" t="s">
+      <c r="H250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14">
+      <c r="A251" t="s">
+        <v>83</v>
+      </c>
+      <c r="C251" t="s">
+        <v>111</v>
+      </c>
+      <c r="D251">
+        <v>1</v>
+      </c>
+      <c r="E251">
+        <v>1</v>
+      </c>
+      <c r="G251">
+        <v>1</v>
+      </c>
+      <c r="M251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14">
+      <c r="A252" t="s">
+        <v>83</v>
+      </c>
+      <c r="C252" t="s">
+        <v>114</v>
+      </c>
+      <c r="D252">
+        <v>1</v>
+      </c>
+      <c r="G252">
+        <v>1</v>
+      </c>
+      <c r="M252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14">
+      <c r="A253" t="s">
+        <v>83</v>
+      </c>
+      <c r="C253" t="s">
+        <v>148</v>
+      </c>
+      <c r="D253">
+        <v>1</v>
+      </c>
+      <c r="G253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14">
+      <c r="A254" t="s">
+        <v>83</v>
+      </c>
+      <c r="C254" t="s">
+        <v>136</v>
+      </c>
+      <c r="D254">
+        <v>1</v>
+      </c>
+      <c r="G254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14">
+      <c r="A255" t="s">
+        <v>83</v>
+      </c>
+      <c r="C255" t="s">
+        <v>190</v>
+      </c>
+      <c r="M255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14">
+      <c r="A256" t="s">
+        <v>83</v>
+      </c>
+      <c r="B256">
+        <v>1</v>
+      </c>
+      <c r="C256" t="s">
+        <v>217</v>
+      </c>
+      <c r="N256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14">
+      <c r="A257" t="s">
+        <v>83</v>
+      </c>
+      <c r="B257">
+        <v>1</v>
+      </c>
+      <c r="C257" t="s">
+        <v>218</v>
+      </c>
+      <c r="N257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14">
+      <c r="A258" t="s">
+        <v>83</v>
+      </c>
+      <c r="B258">
+        <v>1</v>
+      </c>
+      <c r="C258" t="s">
+        <v>219</v>
+      </c>
+      <c r="N258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14">
+      <c r="A259" t="s">
+        <v>83</v>
+      </c>
+      <c r="B259">
+        <v>1</v>
+      </c>
+      <c r="C259" t="s">
+        <v>220</v>
+      </c>
+      <c r="N259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14">
+      <c r="A260" t="s">
+        <v>83</v>
+      </c>
+      <c r="B260">
+        <v>1</v>
+      </c>
+      <c r="C260" t="s">
+        <v>221</v>
+      </c>
+      <c r="N260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14">
+      <c r="A261" t="s">
+        <v>83</v>
+      </c>
+      <c r="B261">
+        <v>1</v>
+      </c>
+      <c r="C261" t="s">
+        <v>222</v>
+      </c>
+      <c r="N261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14">
+      <c r="A262" t="s">
+        <v>83</v>
+      </c>
+      <c r="B262">
+        <v>1</v>
+      </c>
+      <c r="C262" t="s">
+        <v>223</v>
+      </c>
+      <c r="N262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14">
+      <c r="A263" t="s">
+        <v>83</v>
+      </c>
+      <c r="C263" t="s">
+        <v>172</v>
+      </c>
+      <c r="G263">
+        <v>1</v>
+      </c>
+      <c r="M263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14">
+      <c r="A264" t="s">
+        <v>83</v>
+      </c>
+      <c r="C264" t="s">
+        <v>207</v>
+      </c>
+      <c r="M264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14">
+      <c r="A265" t="s">
+        <v>83</v>
+      </c>
+      <c r="C265" t="s">
+        <v>124</v>
+      </c>
+      <c r="D265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14">
+      <c r="A266" t="s">
+        <v>83</v>
+      </c>
+      <c r="C266" t="s">
+        <v>224</v>
+      </c>
+      <c r="D266">
+        <v>1</v>
+      </c>
+      <c r="G266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14">
+      <c r="A267" t="s">
+        <v>83</v>
+      </c>
+      <c r="C267" t="s">
         <v>121</v>
       </c>
-      <c r="E204">
-        <v>1</v>
-      </c>
-      <c r="G204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>184</v>
-      </c>
-      <c r="C205" t="s">
-        <v>94</v>
-      </c>
-      <c r="E205">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>184</v>
-      </c>
-      <c r="C206" t="s">
+    </row>
+    <row r="268" spans="1:14">
+      <c r="A268" t="s">
+        <v>83</v>
+      </c>
+      <c r="C268" t="s">
+        <v>215</v>
+      </c>
+      <c r="D268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14">
+      <c r="A269" t="s">
+        <v>83</v>
+      </c>
+      <c r="C269" t="s">
+        <v>173</v>
+      </c>
+      <c r="D269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14">
+      <c r="A270" t="s">
+        <v>83</v>
+      </c>
+      <c r="C270" t="s">
+        <v>154</v>
+      </c>
+      <c r="G270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14">
+      <c r="A271" t="s">
+        <v>83</v>
+      </c>
+      <c r="C271" t="s">
+        <v>147</v>
+      </c>
+      <c r="E271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14">
+      <c r="A272" t="s">
+        <v>83</v>
+      </c>
+      <c r="C272" t="s">
+        <v>159</v>
+      </c>
+      <c r="F272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14">
+      <c r="A273" t="s">
+        <v>87</v>
+      </c>
+      <c r="C273" t="s">
+        <v>136</v>
+      </c>
+      <c r="G273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14">
+      <c r="A274" t="s">
+        <v>87</v>
+      </c>
+      <c r="C274" t="s">
+        <v>111</v>
+      </c>
+      <c r="G274">
+        <v>1</v>
+      </c>
+      <c r="H274">
+        <v>1</v>
+      </c>
+      <c r="N274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14">
+      <c r="A275" t="s">
+        <v>87</v>
+      </c>
+      <c r="C275" t="s">
         <v>114</v>
       </c>
-      <c r="D206">
-        <v>1</v>
-      </c>
-      <c r="E206">
-        <v>1</v>
-      </c>
-      <c r="F206">
-        <v>1</v>
-      </c>
-      <c r="G206">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>184</v>
-      </c>
-      <c r="C207" t="s">
-        <v>123</v>
-      </c>
-      <c r="F207">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>184</v>
-      </c>
-      <c r="C208" t="s">
-        <v>185</v>
-      </c>
-      <c r="E208">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>184</v>
-      </c>
-      <c r="C209" t="s">
+      <c r="G275">
+        <v>1</v>
+      </c>
+      <c r="H275">
+        <v>1</v>
+      </c>
+      <c r="N275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14">
+      <c r="A276" t="s">
         <v>87</v>
       </c>
-      <c r="D209">
-        <v>1</v>
-      </c>
-      <c r="F209">
-        <v>1</v>
-      </c>
-      <c r="G209">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>184</v>
-      </c>
-      <c r="C210" t="s">
-        <v>109</v>
-      </c>
-      <c r="G210">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
-        <v>186</v>
-      </c>
-      <c r="C211" t="s">
+      <c r="C276" t="s">
+        <v>182</v>
+      </c>
+      <c r="H276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14">
+      <c r="A277" t="s">
         <v>87</v>
       </c>
-      <c r="G211">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>186</v>
-      </c>
-      <c r="C212" t="s">
-        <v>84</v>
-      </c>
-      <c r="G212">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
-        <v>186</v>
-      </c>
-      <c r="C213" t="s">
-        <v>109</v>
-      </c>
-      <c r="G213">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
-        <v>186</v>
-      </c>
-      <c r="C214" t="s">
+      <c r="C277" t="s">
+        <v>225</v>
+      </c>
+      <c r="H277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14">
+      <c r="A278" t="s">
+        <v>87</v>
+      </c>
+      <c r="C278" t="s">
+        <v>173</v>
+      </c>
+      <c r="H278">
+        <v>1</v>
+      </c>
+      <c r="N278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14">
+      <c r="A279" t="s">
+        <v>87</v>
+      </c>
+      <c r="C279" t="s">
+        <v>152</v>
+      </c>
+      <c r="H279">
+        <v>1</v>
+      </c>
+      <c r="N279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14">
+      <c r="A280" t="s">
+        <v>87</v>
+      </c>
+      <c r="C280" t="s">
+        <v>121</v>
+      </c>
+      <c r="H280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14">
+      <c r="A281" t="s">
+        <v>87</v>
+      </c>
+      <c r="C281" t="s">
+        <v>157</v>
+      </c>
+      <c r="H281">
+        <v>1</v>
+      </c>
+      <c r="N281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14">
+      <c r="A282" t="s">
+        <v>87</v>
+      </c>
+      <c r="C282" t="s">
+        <v>148</v>
+      </c>
+      <c r="G282">
+        <v>1</v>
+      </c>
+      <c r="H282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14">
+      <c r="A283" t="s">
+        <v>87</v>
+      </c>
+      <c r="C283" t="s">
+        <v>174</v>
+      </c>
+      <c r="H283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14">
+      <c r="A284" t="s">
+        <v>87</v>
+      </c>
+      <c r="C284" t="s">
+        <v>147</v>
+      </c>
+      <c r="G284">
+        <v>1</v>
+      </c>
+      <c r="H284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14">
+      <c r="A285" t="s">
+        <v>87</v>
+      </c>
+      <c r="C285" t="s">
+        <v>226</v>
+      </c>
+      <c r="H285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14">
+      <c r="A286" t="s">
+        <v>87</v>
+      </c>
+      <c r="C286" t="s">
+        <v>227</v>
+      </c>
+      <c r="N286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14">
+      <c r="A287" t="s">
+        <v>87</v>
+      </c>
+      <c r="C287" t="s">
+        <v>141</v>
+      </c>
+      <c r="G287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14">
+      <c r="A288" t="s">
+        <v>87</v>
+      </c>
+      <c r="C288" t="s">
+        <v>122</v>
+      </c>
+      <c r="N288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14">
+      <c r="A289" t="s">
+        <v>87</v>
+      </c>
+      <c r="C289" t="s">
+        <v>138</v>
+      </c>
+      <c r="N289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14">
+      <c r="A290" t="s">
+        <v>87</v>
+      </c>
+      <c r="C290" t="s">
+        <v>228</v>
+      </c>
+      <c r="N290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14">
+      <c r="A291" t="s">
+        <v>90</v>
+      </c>
+      <c r="C291" t="s">
+        <v>121</v>
+      </c>
+      <c r="H291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14">
+      <c r="A292" t="s">
+        <v>90</v>
+      </c>
+      <c r="C292" t="s">
+        <v>111</v>
+      </c>
+      <c r="G292">
+        <v>1</v>
+      </c>
+      <c r="H292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14">
+      <c r="A293" t="s">
+        <v>90</v>
+      </c>
+      <c r="C293" t="s">
+        <v>147</v>
+      </c>
+      <c r="H293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14">
+      <c r="A294" t="s">
+        <v>90</v>
+      </c>
+      <c r="C294" t="s">
+        <v>207</v>
+      </c>
+      <c r="H294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14">
+      <c r="A295" t="s">
+        <v>90</v>
+      </c>
+      <c r="C295" t="s">
+        <v>172</v>
+      </c>
+      <c r="H295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14">
+      <c r="A296" t="s">
+        <v>90</v>
+      </c>
+      <c r="C296" t="s">
+        <v>148</v>
+      </c>
+      <c r="H296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14">
+      <c r="A297" t="s">
+        <v>90</v>
+      </c>
+      <c r="C297" t="s">
+        <v>201</v>
+      </c>
+      <c r="H297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14">
+      <c r="A298" t="s">
+        <v>90</v>
+      </c>
+      <c r="C298" t="s">
+        <v>136</v>
+      </c>
+      <c r="G298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14">
+      <c r="A299" t="s">
+        <v>90</v>
+      </c>
+      <c r="C299" t="s">
+        <v>150</v>
+      </c>
+      <c r="H299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14">
+      <c r="A300" t="s">
+        <v>93</v>
+      </c>
+      <c r="C300" t="s">
+        <v>111</v>
+      </c>
+      <c r="G300">
+        <v>1</v>
+      </c>
+      <c r="H300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14">
+      <c r="A301" t="s">
+        <v>93</v>
+      </c>
+      <c r="C301" t="s">
+        <v>147</v>
+      </c>
+      <c r="G301">
+        <v>1</v>
+      </c>
+      <c r="H301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14">
+      <c r="A302" t="s">
+        <v>93</v>
+      </c>
+      <c r="C302" t="s">
+        <v>121</v>
+      </c>
+      <c r="G302">
+        <v>1</v>
+      </c>
+      <c r="H302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14">
+      <c r="A303" t="s">
+        <v>93</v>
+      </c>
+      <c r="C303" t="s">
+        <v>148</v>
+      </c>
+      <c r="G303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14">
+      <c r="A304" t="s">
+        <v>93</v>
+      </c>
+      <c r="C304" t="s">
         <v>114</v>
       </c>
-      <c r="E214">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
-        <v>190</v>
-      </c>
-      <c r="C215" t="s">
-        <v>109</v>
-      </c>
-      <c r="G215">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A216" t="s">
-        <v>190</v>
-      </c>
-      <c r="C216" t="s">
-        <v>87</v>
-      </c>
-      <c r="G216">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A217" t="s">
-        <v>192</v>
-      </c>
-      <c r="C217" t="s">
-        <v>84</v>
-      </c>
-      <c r="G217">
-        <v>1</v>
-      </c>
-      <c r="H217">
-        <v>1</v>
-      </c>
-      <c r="M217">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A218" t="s">
-        <v>192</v>
-      </c>
-      <c r="C218" t="s">
-        <v>174</v>
-      </c>
-      <c r="G218">
-        <v>1</v>
-      </c>
-      <c r="H218">
-        <v>1</v>
-      </c>
-      <c r="M218">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A219" t="s">
-        <v>192</v>
-      </c>
-      <c r="C219" t="s">
-        <v>94</v>
-      </c>
-      <c r="H219">
-        <v>1</v>
-      </c>
-      <c r="M219">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A220" t="s">
-        <v>192</v>
-      </c>
-      <c r="C220" t="s">
-        <v>179</v>
-      </c>
-      <c r="H220">
-        <v>1</v>
-      </c>
-      <c r="M220">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A221" t="s">
-        <v>192</v>
-      </c>
-      <c r="C221" t="s">
-        <v>125</v>
-      </c>
-      <c r="G221">
-        <v>1</v>
-      </c>
-      <c r="M221">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A222" t="s">
-        <v>192</v>
-      </c>
-      <c r="C222" t="s">
-        <v>121</v>
-      </c>
-      <c r="H222">
-        <v>1</v>
-      </c>
-      <c r="M222">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A223" t="s">
-        <v>192</v>
-      </c>
-      <c r="C223" t="s">
-        <v>181</v>
-      </c>
-      <c r="M223">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A224" t="s">
-        <v>192</v>
-      </c>
-      <c r="C224" t="s">
-        <v>145</v>
-      </c>
-      <c r="H224">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A225" t="s">
-        <v>192</v>
-      </c>
-      <c r="C225" t="s">
-        <v>87</v>
-      </c>
-      <c r="G225">
-        <v>1</v>
-      </c>
-      <c r="H225">
-        <v>1</v>
-      </c>
-      <c r="M225">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
-        <v>192</v>
-      </c>
-      <c r="C226" t="s">
-        <v>105</v>
-      </c>
-      <c r="M226">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A227" t="s">
-        <v>192</v>
-      </c>
-      <c r="C227" t="s">
-        <v>126</v>
-      </c>
-      <c r="H227">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A228" t="s">
-        <v>192</v>
-      </c>
-      <c r="C228" t="s">
-        <v>120</v>
-      </c>
-      <c r="H228">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
-        <v>192</v>
-      </c>
-      <c r="C229" t="s">
-        <v>130</v>
-      </c>
-      <c r="H229">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A230" t="s">
-        <v>192</v>
-      </c>
-      <c r="C230" t="s">
-        <v>123</v>
-      </c>
-      <c r="H230">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A231" t="s">
-        <v>192</v>
-      </c>
-      <c r="C231" t="s">
-        <v>195</v>
-      </c>
-      <c r="H231">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
-        <v>192</v>
-      </c>
-      <c r="C232" t="s">
-        <v>127</v>
-      </c>
-      <c r="H232">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
-        <v>192</v>
-      </c>
-      <c r="C233" t="s">
-        <v>109</v>
-      </c>
-      <c r="G233">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
-        <v>196</v>
-      </c>
-      <c r="C234" t="s">
-        <v>94</v>
-      </c>
-      <c r="E234">
-        <v>1</v>
-      </c>
-      <c r="G234">
-        <v>1</v>
-      </c>
-      <c r="H234">
-        <v>1</v>
-      </c>
-      <c r="M234">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A235" t="s">
-        <v>196</v>
-      </c>
-      <c r="C235" t="s">
-        <v>84</v>
-      </c>
-      <c r="E235">
-        <v>1</v>
-      </c>
-      <c r="G235">
-        <v>1</v>
-      </c>
-      <c r="H235">
-        <v>1</v>
-      </c>
-      <c r="M235">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
-        <v>196</v>
-      </c>
-      <c r="C236" t="s">
-        <v>87</v>
-      </c>
-      <c r="E236">
-        <v>1</v>
-      </c>
-      <c r="G236">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A237" t="s">
-        <v>196</v>
-      </c>
-      <c r="C237" t="s">
-        <v>198</v>
-      </c>
-      <c r="E237">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A238" t="s">
-        <v>196</v>
-      </c>
-      <c r="C238" t="s">
-        <v>120</v>
-      </c>
-      <c r="E238">
-        <v>1</v>
-      </c>
-      <c r="G238">
-        <v>1</v>
-      </c>
-      <c r="H238">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
-        <v>196</v>
-      </c>
-      <c r="C239" t="s">
-        <v>109</v>
-      </c>
-      <c r="E239">
-        <v>1</v>
-      </c>
-      <c r="G239">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A240" t="s">
-        <v>196</v>
-      </c>
-      <c r="C240" t="s">
-        <v>121</v>
-      </c>
-      <c r="E240">
-        <v>1</v>
-      </c>
-      <c r="G240">
-        <v>1</v>
-      </c>
-      <c r="H240">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
-        <v>196</v>
-      </c>
-      <c r="C241" t="s">
-        <v>90</v>
-      </c>
-      <c r="E241">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A242" t="s">
-        <v>196</v>
-      </c>
-      <c r="C242" t="s">
-        <v>182</v>
-      </c>
-      <c r="E242">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A243" t="s">
-        <v>196</v>
-      </c>
-      <c r="C243" t="s">
-        <v>127</v>
-      </c>
-      <c r="E243">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A244" t="s">
-        <v>196</v>
-      </c>
-      <c r="C244" t="s">
-        <v>199</v>
-      </c>
-      <c r="E244">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A245" t="s">
-        <v>196</v>
-      </c>
-      <c r="C245" t="s">
-        <v>200</v>
-      </c>
-      <c r="E245">
-        <v>1</v>
-      </c>
-      <c r="G245">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A246" t="s">
-        <v>196</v>
-      </c>
-      <c r="C246" t="s">
+      <c r="G304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11">
+      <c r="A305" t="s">
+        <v>93</v>
+      </c>
+      <c r="C305" t="s">
         <v>201</v>
       </c>
-      <c r="E246">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A247" t="s">
-        <v>196</v>
-      </c>
-      <c r="C247" t="s">
-        <v>123</v>
-      </c>
-      <c r="G247">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A248" t="s">
-        <v>196</v>
-      </c>
-      <c r="C248" t="s">
-        <v>148</v>
-      </c>
-      <c r="G248">
-        <v>1</v>
-      </c>
-      <c r="M248">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
-        <v>196</v>
-      </c>
-      <c r="C249" t="s">
-        <v>114</v>
-      </c>
-      <c r="E249">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A250" t="s">
-        <v>196</v>
-      </c>
-      <c r="C250" t="s">
-        <v>157</v>
-      </c>
-      <c r="H250">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A251" t="s">
-        <v>202</v>
-      </c>
-      <c r="C251" t="s">
-        <v>84</v>
-      </c>
-      <c r="D251">
-        <v>1</v>
-      </c>
-      <c r="E251">
-        <v>1</v>
-      </c>
-      <c r="G251">
-        <v>1</v>
-      </c>
-      <c r="M251">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A252" t="s">
-        <v>202</v>
-      </c>
-      <c r="C252" t="s">
-        <v>87</v>
-      </c>
-      <c r="D252">
-        <v>1</v>
-      </c>
-      <c r="G252">
-        <v>1</v>
-      </c>
-      <c r="M252">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A253" t="s">
-        <v>202</v>
-      </c>
-      <c r="C253" t="s">
-        <v>121</v>
-      </c>
-      <c r="D253">
-        <v>1</v>
-      </c>
-      <c r="G253">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A254" t="s">
-        <v>202</v>
-      </c>
-      <c r="C254" t="s">
-        <v>109</v>
-      </c>
-      <c r="D254">
-        <v>1</v>
-      </c>
-      <c r="G254">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A255" t="s">
-        <v>202</v>
-      </c>
-      <c r="C255" t="s">
-        <v>163</v>
-      </c>
-      <c r="M255">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
-        <v>202</v>
-      </c>
-      <c r="B256">
-        <v>1</v>
-      </c>
-      <c r="C256" t="s">
-        <v>206</v>
-      </c>
-      <c r="N256">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A257" t="s">
-        <v>202</v>
-      </c>
-      <c r="B257">
-        <v>1</v>
-      </c>
-      <c r="C257" t="s">
+      <c r="G305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11">
+      <c r="A306" t="s">
+        <v>93</v>
+      </c>
+      <c r="C306" t="s">
+        <v>172</v>
+      </c>
+      <c r="H306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11">
+      <c r="A307" t="s">
+        <v>93</v>
+      </c>
+      <c r="C307" t="s">
         <v>207</v>
       </c>
-      <c r="N257">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A258" t="s">
-        <v>202</v>
-      </c>
-      <c r="B258">
-        <v>1</v>
-      </c>
-      <c r="C258" t="s">
-        <v>208</v>
-      </c>
-      <c r="N258">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A259" t="s">
-        <v>202</v>
-      </c>
-      <c r="B259">
-        <v>1</v>
-      </c>
-      <c r="C259" t="s">
-        <v>209</v>
-      </c>
-      <c r="N259">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A260" t="s">
-        <v>202</v>
-      </c>
-      <c r="B260">
-        <v>1</v>
-      </c>
-      <c r="C260" t="s">
-        <v>210</v>
-      </c>
-      <c r="N260">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A261" t="s">
-        <v>202</v>
-      </c>
-      <c r="B261">
-        <v>1</v>
-      </c>
-      <c r="C261" t="s">
-        <v>211</v>
-      </c>
-      <c r="N261">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A262" t="s">
-        <v>202</v>
-      </c>
-      <c r="B262">
-        <v>1</v>
-      </c>
-      <c r="C262" t="s">
-        <v>212</v>
-      </c>
-      <c r="N262">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A263" t="s">
-        <v>202</v>
-      </c>
-      <c r="C263" t="s">
-        <v>145</v>
-      </c>
-      <c r="G263">
-        <v>1</v>
-      </c>
-      <c r="M263">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A264" t="s">
-        <v>202</v>
-      </c>
-      <c r="C264" t="s">
-        <v>180</v>
-      </c>
-      <c r="M264">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A265" t="s">
-        <v>202</v>
-      </c>
-      <c r="C265" t="s">
-        <v>97</v>
-      </c>
-      <c r="D265">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A266" t="s">
-        <v>202</v>
-      </c>
-      <c r="C266" t="s">
-        <v>213</v>
-      </c>
-      <c r="D266">
-        <v>1</v>
-      </c>
-      <c r="G266">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A267" t="s">
-        <v>202</v>
-      </c>
-      <c r="C267" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A268" t="s">
-        <v>202</v>
-      </c>
-      <c r="C268" t="s">
-        <v>200</v>
-      </c>
-      <c r="D268">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A269" t="s">
-        <v>202</v>
-      </c>
-      <c r="C269" t="s">
-        <v>146</v>
-      </c>
-      <c r="D269">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A270" t="s">
-        <v>202</v>
-      </c>
-      <c r="C270" t="s">
-        <v>127</v>
-      </c>
-      <c r="G270">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A271" t="s">
-        <v>202</v>
-      </c>
-      <c r="C271" t="s">
-        <v>120</v>
-      </c>
-      <c r="E271">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A272" t="s">
-        <v>202</v>
-      </c>
-      <c r="C272" t="s">
-        <v>132</v>
-      </c>
-      <c r="F272">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
-        <v>214</v>
-      </c>
-      <c r="C273" t="s">
-        <v>109</v>
-      </c>
-      <c r="G273">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
-        <v>214</v>
-      </c>
-      <c r="C274" t="s">
-        <v>84</v>
-      </c>
-      <c r="G274">
-        <v>1</v>
-      </c>
-      <c r="H274">
-        <v>1</v>
-      </c>
-      <c r="N274">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
-        <v>214</v>
-      </c>
-      <c r="C275" t="s">
-        <v>87</v>
-      </c>
-      <c r="G275">
-        <v>1</v>
-      </c>
-      <c r="H275">
-        <v>1</v>
-      </c>
-      <c r="N275">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A276" t="s">
-        <v>214</v>
-      </c>
-      <c r="C276" t="s">
-        <v>155</v>
-      </c>
-      <c r="H276">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
-        <v>214</v>
-      </c>
-      <c r="C277" t="s">
-        <v>217</v>
-      </c>
-      <c r="H277">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A278" t="s">
-        <v>214</v>
-      </c>
-      <c r="C278" t="s">
-        <v>146</v>
-      </c>
-      <c r="H278">
-        <v>1</v>
-      </c>
-      <c r="N278">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A279" t="s">
-        <v>214</v>
-      </c>
-      <c r="C279" t="s">
-        <v>125</v>
-      </c>
-      <c r="H279">
-        <v>1</v>
-      </c>
-      <c r="N279">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A280" t="s">
-        <v>214</v>
-      </c>
-      <c r="C280" t="s">
-        <v>94</v>
-      </c>
-      <c r="H280">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
-        <v>214</v>
-      </c>
-      <c r="C281" t="s">
-        <v>130</v>
-      </c>
-      <c r="H281">
-        <v>1</v>
-      </c>
-      <c r="N281">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>214</v>
-      </c>
-      <c r="C282" t="s">
-        <v>121</v>
-      </c>
-      <c r="G282">
-        <v>1</v>
-      </c>
-      <c r="H282">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
-        <v>214</v>
-      </c>
-      <c r="C283" t="s">
-        <v>147</v>
-      </c>
-      <c r="H283">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
-        <v>214</v>
-      </c>
-      <c r="C284" t="s">
-        <v>120</v>
-      </c>
-      <c r="G284">
-        <v>1</v>
-      </c>
-      <c r="H284">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
-        <v>214</v>
-      </c>
-      <c r="C285" t="s">
-        <v>218</v>
-      </c>
-      <c r="H285">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A286" t="s">
-        <v>214</v>
-      </c>
-      <c r="C286" t="s">
-        <v>219</v>
-      </c>
-      <c r="N286">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A287" t="s">
-        <v>214</v>
-      </c>
-      <c r="C287" t="s">
-        <v>114</v>
-      </c>
-      <c r="G287">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A288" t="s">
-        <v>214</v>
-      </c>
-      <c r="C288" t="s">
+      <c r="G307">
+        <v>1</v>
+      </c>
+      <c r="H307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11">
+      <c r="A308" t="s">
+        <v>93</v>
+      </c>
+      <c r="C308" t="s">
+        <v>150</v>
+      </c>
+      <c r="H308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11">
+      <c r="A309" t="s">
         <v>95</v>
       </c>
-      <c r="N288">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
-        <v>214</v>
-      </c>
-      <c r="C289" t="s">
+      <c r="C309" t="s">
         <v>111</v>
       </c>
-      <c r="N289">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A290" t="s">
-        <v>214</v>
-      </c>
-      <c r="C290" t="s">
-        <v>220</v>
-      </c>
-      <c r="N290">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
-        <v>221</v>
-      </c>
-      <c r="C291" t="s">
-        <v>94</v>
-      </c>
-      <c r="H291">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
-        <v>221</v>
-      </c>
-      <c r="C292" t="s">
-        <v>84</v>
-      </c>
-      <c r="G292">
-        <v>1</v>
-      </c>
-      <c r="H292">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
-        <v>221</v>
-      </c>
-      <c r="C293" t="s">
-        <v>120</v>
-      </c>
-      <c r="H293">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>221</v>
-      </c>
-      <c r="C294" t="s">
-        <v>180</v>
-      </c>
-      <c r="H294">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
-        <v>221</v>
-      </c>
-      <c r="C295" t="s">
-        <v>145</v>
-      </c>
-      <c r="H295">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
-        <v>221</v>
-      </c>
-      <c r="C296" t="s">
-        <v>121</v>
-      </c>
-      <c r="H296">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
-        <v>221</v>
-      </c>
-      <c r="C297" t="s">
-        <v>174</v>
-      </c>
-      <c r="H297">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
-        <v>221</v>
-      </c>
-      <c r="C298" t="s">
-        <v>109</v>
-      </c>
-      <c r="G298">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A299" t="s">
-        <v>221</v>
-      </c>
-      <c r="C299" t="s">
-        <v>123</v>
-      </c>
-      <c r="H299">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A300" t="s">
-        <v>222</v>
-      </c>
-      <c r="C300" t="s">
-        <v>84</v>
-      </c>
-      <c r="G300">
-        <v>1</v>
-      </c>
-      <c r="H300">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A301" t="s">
-        <v>222</v>
-      </c>
-      <c r="C301" t="s">
-        <v>120</v>
-      </c>
-      <c r="G301">
-        <v>1</v>
-      </c>
-      <c r="H301">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
-        <v>222</v>
-      </c>
-      <c r="C302" t="s">
-        <v>94</v>
-      </c>
-      <c r="G302">
-        <v>1</v>
-      </c>
-      <c r="H302">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A303" t="s">
-        <v>222</v>
-      </c>
-      <c r="C303" t="s">
-        <v>121</v>
-      </c>
-      <c r="G303">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
-        <v>222</v>
-      </c>
-      <c r="C304" t="s">
-        <v>87</v>
-      </c>
-      <c r="G304">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
-        <v>222</v>
-      </c>
-      <c r="C305" t="s">
-        <v>174</v>
-      </c>
-      <c r="G305">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A306" t="s">
-        <v>222</v>
-      </c>
-      <c r="C306" t="s">
-        <v>145</v>
-      </c>
-      <c r="H306">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A307" t="s">
-        <v>222</v>
-      </c>
-      <c r="C307" t="s">
-        <v>180</v>
-      </c>
-      <c r="G307">
-        <v>1</v>
-      </c>
-      <c r="H307">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A308" t="s">
-        <v>222</v>
-      </c>
-      <c r="C308" t="s">
-        <v>123</v>
-      </c>
-      <c r="H308">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A309" t="s">
-        <v>226</v>
-      </c>
-      <c r="C309" t="s">
-        <v>84</v>
-      </c>
       <c r="E309">
         <v>1</v>
       </c>
@@ -6499,9 +6495,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11">
       <c r="A310" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C310" t="s">
         <v>229</v>
@@ -6510,12 +6506,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11">
       <c r="A311" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C311" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="G311">
         <v>1</v>
@@ -6524,12 +6520,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11">
       <c r="A312" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C312" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -6538,12 +6534,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11">
       <c r="A313" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C313" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="E313">
         <v>1</v>
@@ -6555,12 +6551,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11">
       <c r="A314" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C314" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E314">
         <v>1</v>
@@ -6572,45 +6568,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11">
       <c r="A315" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C315" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E315">
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11">
       <c r="A316" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C316" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="E316">
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11">
       <c r="A317" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C317" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="E317">
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11">
       <c r="A318" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C318" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E318">
         <v>1</v>
@@ -6619,9 +6615,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11">
       <c r="A319" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C319" t="s">
         <v>230</v>
@@ -6630,9 +6626,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11">
       <c r="A320" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C320" t="s">
         <v>231</v>
@@ -6641,12 +6637,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11">
       <c r="A321" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C321" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G321">
         <v>1</v>
@@ -6655,20 +6651,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11">
       <c r="A322" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C322" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="K322">
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11">
       <c r="A323" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C323" t="s">
         <v>232</v>
@@ -6677,31 +6673,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11">
       <c r="A324" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C324" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G324">
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11">
       <c r="A325" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C325" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="K325">
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11">
       <c r="A326" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C326" t="s">
         <v>233</v>
@@ -6710,42 +6706,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11">
       <c r="A327" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C327" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="K327">
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11">
       <c r="A328" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C328" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="K328">
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11">
       <c r="A329" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C329" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="K329">
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11">
       <c r="A330" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C330" t="s">
         <v>234</v>
@@ -6754,9 +6750,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11">
       <c r="A331" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="C331" t="s">
         <v>235</v>
@@ -6765,12 +6761,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11">
       <c r="A332" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="B332" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C332" t="s">
         <v>236</v>
@@ -6779,9 +6775,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11">
       <c r="A333" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="B333">
         <v>1</v>
@@ -6793,9 +6789,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11">
       <c r="A334" t="s">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="B334">
         <v>1</v>
@@ -6813,26 +6809,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0278717-252d-455f-9297-341259384352">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="67fd2e6b-9b4b-488b-ae5d-884371a2c380" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F98E057C991C64EA8C44B2688F4F4E8" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="205ac32a36de600e2ab9bca4f1502e82">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0278717-252d-455f-9297-341259384352" xmlns:ns3="67fd2e6b-9b4b-488b-ae5d-884371a2c380" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="423e538afa53ae88b73bb7a22e6ab62a" ns2:_="" ns3:_="">
     <xsd:import namespace="b0278717-252d-455f-9297-341259384352"/>
@@ -7021,46 +6997,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0278717-252d-455f-9297-341259384352">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="67fd2e6b-9b4b-488b-ae5d-884371a2c380" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87681022-589A-4D48-98F7-B0B4DE2A50CA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="67fd2e6b-9b4b-488b-ae5d-884371a2c380"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b0278717-252d-455f-9297-341259384352"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75991279-CDFD-432A-85F7-9F9EBD8C5574}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5032AD0-6421-44B7-9938-A4A0BC003650}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5032AD0-6421-44B7-9938-A4A0BC003650}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75991279-CDFD-432A-85F7-9F9EBD8C5574}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b0278717-252d-455f-9297-341259384352"/>
-    <ds:schemaRef ds:uri="67fd2e6b-9b4b-488b-ae5d-884371a2c380"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87681022-589A-4D48-98F7-B0B4DE2A50CA}"/>
 </file>
--- a/Raw/SDMR_FIELD.xlsx
+++ b/Raw/SDMR_FIELD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mnhnfr.sharepoint.com/sites/ParisWildness/Documents partages/General/Data/Vegetation data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c0c9e545cc4bad76/Bureau/STAGE/Stage_M1_UWS/Raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D7609B0-7474-441A-99CB-6AD4A8300BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{C9934450-2725-4EFF-AAE3-91E8A0A1F6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14C80FAB-46D7-494C-B36A-830CBF3960B1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="transect" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="307">
   <si>
     <t>Largeur du trottoir</t>
   </si>
@@ -324,15 +324,45 @@
     <t>A nouveau terre-plein entre 2 routes, mais piéton et avec bancs ! Habitats : pied d'arbre isolé car un cerle en métal les délimite, et un chemin les relie</t>
   </si>
   <si>
-    <t>Buf</t>
-  </si>
-  <si>
     <t>15bis rue Buffon</t>
   </si>
   <si>
     <t>Test</t>
   </si>
   <si>
+    <t>7E_COG</t>
+  </si>
+  <si>
+    <t>8 rue Cognac-Jacq</t>
+  </si>
+  <si>
+    <t>7E_COU</t>
+  </si>
+  <si>
+    <t>Rue de Courty</t>
+  </si>
+  <si>
+    <t>7E_VER</t>
+  </si>
+  <si>
+    <t>49 rue de Verneuil</t>
+  </si>
+  <si>
+    <t>7E_MON</t>
+  </si>
+  <si>
+    <t>19E_TAN</t>
+  </si>
+  <si>
+    <t>Rue Tandou</t>
+  </si>
+  <si>
+    <t>19E_LAL</t>
+  </si>
+  <si>
+    <t>Rue Lally</t>
+  </si>
+  <si>
     <t>Horticole</t>
   </si>
   <si>
@@ -754,13 +784,187 @@
   </si>
   <si>
     <t>40-45 horticoles</t>
+  </si>
+  <si>
+    <t>Erigeron karvinskianus</t>
+  </si>
+  <si>
+    <t>Verbenaceae sp</t>
+  </si>
+  <si>
+    <t>Ceratostigma sp</t>
+  </si>
+  <si>
+    <t>Forythra sp</t>
+  </si>
+  <si>
+    <t>Spartium junceum</t>
+  </si>
+  <si>
+    <t>Agapanthus</t>
+  </si>
+  <si>
+    <t>Eonymus sp</t>
+  </si>
+  <si>
+    <t>Saleria microphylla</t>
+  </si>
+  <si>
+    <t>Buisson sp</t>
+  </si>
+  <si>
+    <t>Hibiscus sp</t>
+  </si>
+  <si>
+    <t>Euphorbia sp</t>
+  </si>
+  <si>
+    <t>Phlomis fruticosa</t>
+  </si>
+  <si>
+    <t>Heuchera sanguinea</t>
+  </si>
+  <si>
+    <t>Phillyrea angustifolia</t>
+  </si>
+  <si>
+    <t>Geranium macrorrhizum</t>
+  </si>
+  <si>
+    <t>Syringa persica</t>
+  </si>
+  <si>
+    <t>Narcissus sp</t>
+  </si>
+  <si>
+    <t>Tanacetum corymbosum</t>
+  </si>
+  <si>
+    <t>Cicerbita ?</t>
+  </si>
+  <si>
+    <t>Tradescantia sp</t>
+  </si>
+  <si>
+    <t>Dianthus (plumarius)</t>
+  </si>
+  <si>
+    <t>Dianthus barbatus</t>
+  </si>
+  <si>
+    <t>Geranium endrossi</t>
+  </si>
+  <si>
+    <t>Euphorbia peplus ?</t>
+  </si>
+  <si>
+    <t>Erysimum cheiri</t>
+  </si>
+  <si>
+    <t>Jacobaea maritima</t>
+  </si>
+  <si>
+    <t>Ornithogalum umbellatum</t>
+  </si>
+  <si>
+    <t>Asparagus sp</t>
+  </si>
+  <si>
+    <t>Anemone hupehensis</t>
+  </si>
+  <si>
+    <t>Erysimum sp</t>
+  </si>
+  <si>
+    <t>Solanum pseudocepsium</t>
+  </si>
+  <si>
+    <t>h1</t>
+  </si>
+  <si>
+    <t>h2</t>
+  </si>
+  <si>
+    <t>h3</t>
+  </si>
+  <si>
+    <t>h4</t>
+  </si>
+  <si>
+    <t>h5</t>
+  </si>
+  <si>
+    <t>h6</t>
+  </si>
+  <si>
+    <t>h7</t>
+  </si>
+  <si>
+    <t>h8</t>
+  </si>
+  <si>
+    <t>h9</t>
+  </si>
+  <si>
+    <t>h10</t>
+  </si>
+  <si>
+    <t>h11</t>
+  </si>
+  <si>
+    <t>h12</t>
+  </si>
+  <si>
+    <t>h13</t>
+  </si>
+  <si>
+    <t>h14</t>
+  </si>
+  <si>
+    <t>h15</t>
+  </si>
+  <si>
+    <t>h16</t>
+  </si>
+  <si>
+    <t>h17</t>
+  </si>
+  <si>
+    <t>Trifolium sp</t>
+  </si>
+  <si>
+    <t>Potentille sp</t>
+  </si>
+  <si>
+    <t>Myosotis sp</t>
+  </si>
+  <si>
+    <t>Impatiens sp</t>
+  </si>
+  <si>
+    <t>h18</t>
+  </si>
+  <si>
+    <t>h19</t>
+  </si>
+  <si>
+    <t>h20</t>
+  </si>
+  <si>
+    <t>arbre</t>
+  </si>
+  <si>
+    <t>Asteraceae sp</t>
+  </si>
+  <si>
+    <t>5E_BUF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -823,9 +1027,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -863,7 +1067,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -969,7 +1173,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1111,7 +1315,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1119,8 +1323,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W25"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:W31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.140625" customWidth="1"/>
@@ -1137,7 +1341,7 @@
     <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="F1" s="4" t="s">
         <v>0</v>
@@ -1157,7 +1361,7 @@
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1228,7 +1432,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="28.9">
+    <row r="3" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -1275,7 +1479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
@@ -1325,7 +1529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -1372,7 +1576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="43.15">
+    <row r="6" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -1425,7 +1629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -1478,7 +1682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>47</v>
       </c>
@@ -1525,7 +1729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
@@ -1572,7 +1776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>53</v>
       </c>
@@ -1622,7 +1826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>55</v>
       </c>
@@ -1675,7 +1879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>61</v>
       </c>
@@ -1722,7 +1926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -1769,7 +1973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="43.15">
+    <row r="14" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>64</v>
       </c>
@@ -1810,7 +2014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="28.9">
+    <row r="15" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -1863,7 +2067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1910,7 +2114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>73</v>
       </c>
@@ -1957,7 +2161,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -2004,7 +2208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="28.9">
+    <row r="19" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -2054,7 +2258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>81</v>
       </c>
@@ -2098,7 +2302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="28.9">
+    <row r="21" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>83</v>
       </c>
@@ -2154,7 +2358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="43.15">
+    <row r="22" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>87</v>
       </c>
@@ -2201,7 +2405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="57.6">
+    <row r="23" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -2248,7 +2452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="72">
+    <row r="24" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -2298,12 +2502,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>306</v>
+      </c>
+      <c r="B25" t="s">
         <v>95</v>
-      </c>
-      <c r="B25" t="s">
-        <v>96</v>
       </c>
       <c r="C25" s="1">
         <v>46125</v>
@@ -2312,7 +2516,7 @@
         <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25">
         <v>9</v>
@@ -2351,6 +2555,324 @@
         <v>1</v>
       </c>
       <c r="T25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26">
+        <v>6</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" t="s">
+        <v>39</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27">
+        <v>2.5</v>
+      </c>
+      <c r="G27">
+        <v>2.5</v>
+      </c>
+      <c r="H27" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28">
+        <v>1.5</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29">
+        <v>3.5</v>
+      </c>
+      <c r="G29">
+        <v>3.5</v>
+      </c>
+      <c r="H29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J29" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" t="s">
+        <v>67</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30">
+        <v>2.5</v>
+      </c>
+      <c r="G30">
+        <v>6</v>
+      </c>
+      <c r="H30" t="s">
+        <v>34</v>
+      </c>
+      <c r="I30" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" t="s">
+        <v>14</v>
+      </c>
+      <c r="L30" t="s">
+        <v>39</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30">
+        <v>1</v>
+      </c>
+      <c r="T30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D31" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31">
+        <v>2.25</v>
+      </c>
+      <c r="G31">
+        <v>2.25</v>
+      </c>
+      <c r="H31" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" t="s">
+        <v>39</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="P31">
         <v>1</v>
       </c>
     </row>
@@ -2365,8 +2887,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B3963A-ED2B-41F3-80D1-989660668753}">
-  <dimension ref="A1:N334"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:N450"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.28515625" customWidth="1"/>
@@ -2379,51 +2901,51 @@
     <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F1" t="s">
         <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="J1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="N1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
@@ -2431,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -2467,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -2475,7 +2997,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -2511,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -2519,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -2555,7 +3077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -2563,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -2599,15 +3121,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -2643,7 +3165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
@@ -2651,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -2687,7 +3209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
@@ -2695,7 +3217,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2731,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
@@ -2739,13 +3261,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>25</v>
       </c>
@@ -2753,68 +3275,68 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="L12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -2822,184 +3344,184 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="L24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="L27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="L31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>25</v>
       </c>
@@ -3007,40 +3529,40 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="L32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -3055,23 +3577,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -3083,12 +3605,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3100,12 +3622,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -3117,45 +3639,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C41" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -3164,23 +3686,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -3189,56 +3711,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C46" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C47" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C48" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C49" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C50" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -3247,34 +3769,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C52" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3283,23 +3805,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C54" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -3308,12 +3830,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C56" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3322,23 +3844,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C58" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -3347,12 +3869,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -3361,23 +3883,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3386,23 +3908,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C62" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3411,34 +3933,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C64" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C65" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G65">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3447,56 +3969,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C67" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C68" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C69" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C70" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D70">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C71" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -3505,7 +4027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>40</v>
       </c>
@@ -3513,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -3522,7 +4044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>40</v>
       </c>
@@ -3530,27 +4052,27 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="K73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B74" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C74" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="K74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>40</v>
       </c>
@@ -3558,13 +4080,13 @@
         <v>1</v>
       </c>
       <c r="C75" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="K75">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>40</v>
       </c>
@@ -3572,13 +4094,13 @@
         <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>40</v>
       </c>
@@ -3586,13 +4108,13 @@
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K77">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>40</v>
       </c>
@@ -3600,13 +4122,13 @@
         <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="K78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>40</v>
       </c>
@@ -3614,32 +4136,32 @@
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="K79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="K80">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3648,12 +4170,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C82" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3662,100 +4184,100 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C83" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G83">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C85" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E85">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C86" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G87">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C88" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C89" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C90" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C91" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -3764,12 +4286,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C92" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -3778,34 +4300,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C93" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G93">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C94" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G94">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C95" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -3814,45 +4336,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C96" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C97" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G97">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C98" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="G98">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C99" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -3861,12 +4383,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C100" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -3875,23 +4397,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C101" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G101">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C102" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -3900,45 +4422,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C103" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C104" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C105" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C106" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -3947,12 +4469,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C107" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -3961,12 +4483,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C108" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -3975,29 +4497,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C109" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="N109">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C110" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="N110">
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>50</v>
       </c>
@@ -4005,32 +4527,32 @@
         <v>1</v>
       </c>
       <c r="C111" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="N111">
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C112" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="N112">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C113" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -4042,12 +4564,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C114" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -4056,34 +4578,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C115" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H115">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C116" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="H116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C117" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -4092,12 +4614,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C118" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -4106,111 +4628,111 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C119" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G119">
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C120" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G120">
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C121" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G121">
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C122" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G122">
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C123" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G123">
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C124" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="H124">
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C125" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="H125">
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C126" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="H126">
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C127" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G127">
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C128" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4222,23 +4744,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C129" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C130" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4250,34 +4772,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C131" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="G131">
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C132" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G132">
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C133" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -4286,45 +4808,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C134" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G134">
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C135" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H135">
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C136" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="H136">
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C137" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -4333,34 +4855,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C138" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H138">
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C139" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="H139">
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C140" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -4372,23 +4894,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C141" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G141">
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C142" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -4400,12 +4922,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C143" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -4414,12 +4936,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C144" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -4431,34 +4953,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C145" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G145">
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C146" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="M146">
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>61</v>
       </c>
       <c r="C147" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -4467,73 +4989,73 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>61</v>
       </c>
       <c r="C148" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G148">
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>61</v>
       </c>
       <c r="C149" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="G149">
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>61</v>
       </c>
       <c r="C150" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G150">
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>61</v>
       </c>
       <c r="C151" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G151">
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>61</v>
       </c>
       <c r="C152" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G152">
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:13">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>61</v>
       </c>
       <c r="C153" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G153">
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>61</v>
       </c>
@@ -4541,7 +5063,7 @@
         <v>1</v>
       </c>
       <c r="C154" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -4550,23 +5072,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>63</v>
       </c>
       <c r="C155" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G155">
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>63</v>
       </c>
       <c r="C156" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -4578,111 +5100,111 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>63</v>
       </c>
       <c r="C157" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H157">
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:13">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>63</v>
       </c>
       <c r="C158" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H158">
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:13">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>63</v>
       </c>
       <c r="C159" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="H159">
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:13">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>63</v>
       </c>
       <c r="C160" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H160">
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>63</v>
       </c>
       <c r="C161" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>63</v>
       </c>
       <c r="C162" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="H162">
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>63</v>
       </c>
       <c r="C163" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="H163">
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>63</v>
       </c>
       <c r="C164" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G164">
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>63</v>
       </c>
       <c r="C165" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G165">
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>64</v>
       </c>
       <c r="C166" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E166">
         <v>1</v>
@@ -4691,12 +5213,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>64</v>
       </c>
       <c r="C167" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -4705,23 +5227,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>64</v>
       </c>
       <c r="C168" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G168">
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>64</v>
       </c>
       <c r="C169" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E169">
         <v>1</v>
@@ -4730,56 +5252,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>64</v>
       </c>
       <c r="C170" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G170">
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>64</v>
       </c>
       <c r="C171" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G171">
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>64</v>
       </c>
       <c r="C172" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G172">
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>64</v>
       </c>
       <c r="C173" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="G173">
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>64</v>
       </c>
       <c r="C174" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E174">
         <v>1</v>
@@ -4788,12 +5310,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>64</v>
       </c>
       <c r="C175" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="E175">
         <v>1</v>
@@ -4802,12 +5324,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>64</v>
       </c>
       <c r="C176" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E176">
         <v>1</v>
@@ -4816,78 +5338,78 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>64</v>
       </c>
       <c r="C177" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G177">
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>64</v>
       </c>
       <c r="C178" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G178">
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>64</v>
       </c>
       <c r="C179" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G179">
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>64</v>
       </c>
       <c r="C180" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G180">
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>64</v>
       </c>
       <c r="C181" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E181">
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>68</v>
       </c>
       <c r="C182" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="I182">
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>68</v>
       </c>
       <c r="C183" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -4899,12 +5421,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>68</v>
       </c>
       <c r="C184" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -4913,34 +5435,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>68</v>
       </c>
       <c r="C185" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="I185">
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>68</v>
       </c>
       <c r="C186" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G186">
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>68</v>
       </c>
       <c r="C187" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E187">
         <v>1</v>
@@ -4949,12 +5471,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>68</v>
       </c>
       <c r="C188" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -4963,34 +5485,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>68</v>
       </c>
       <c r="C189" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="I189">
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>68</v>
       </c>
       <c r="C190" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="I190">
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>68</v>
       </c>
       <c r="C191" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -5002,34 +5524,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>68</v>
       </c>
       <c r="C192" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G192">
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>68</v>
       </c>
       <c r="C193" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G193">
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>68</v>
       </c>
       <c r="C194" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G194">
         <v>1</v>
@@ -5038,100 +5560,100 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>68</v>
       </c>
       <c r="C195" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="I195">
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>68</v>
       </c>
       <c r="C196" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="I196">
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>68</v>
       </c>
       <c r="C197" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="I197">
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>68</v>
       </c>
       <c r="C198" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="I198">
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>68</v>
       </c>
       <c r="C199" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G199">
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>68</v>
       </c>
       <c r="C200" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G200">
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>68</v>
       </c>
       <c r="C201" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G201">
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>68</v>
       </c>
       <c r="C202" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="I202">
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>71</v>
       </c>
       <c r="C203" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -5143,12 +5665,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>71</v>
       </c>
       <c r="C204" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E204">
         <v>1</v>
@@ -5157,23 +5679,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>71</v>
       </c>
       <c r="C205" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E205">
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>71</v>
       </c>
       <c r="C206" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -5188,34 +5710,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>71</v>
       </c>
       <c r="C207" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F207">
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>71</v>
       </c>
       <c r="C208" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="E208">
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>71</v>
       </c>
       <c r="C209" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -5227,89 +5749,89 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>71</v>
       </c>
       <c r="C210" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G210">
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>73</v>
       </c>
       <c r="C211" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G211">
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>73</v>
       </c>
       <c r="C212" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G212">
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>73</v>
       </c>
       <c r="C213" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G213">
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>73</v>
       </c>
       <c r="C214" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E214">
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>76</v>
       </c>
       <c r="C215" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G215">
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>76</v>
       </c>
       <c r="C216" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G216">
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>78</v>
       </c>
       <c r="C217" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G217">
         <v>1</v>
@@ -5321,12 +5843,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>78</v>
       </c>
       <c r="C218" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="G218">
         <v>1</v>
@@ -5338,12 +5860,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>78</v>
       </c>
       <c r="C219" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H219">
         <v>1</v>
@@ -5352,12 +5874,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>78</v>
       </c>
       <c r="C220" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="H220">
         <v>1</v>
@@ -5366,12 +5888,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>78</v>
       </c>
       <c r="C221" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G221">
         <v>1</v>
@@ -5380,12 +5902,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>78</v>
       </c>
       <c r="C222" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="H222">
         <v>1</v>
@@ -5394,34 +5916,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>78</v>
       </c>
       <c r="C223" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="M223">
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>78</v>
       </c>
       <c r="C224" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H224">
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>78</v>
       </c>
       <c r="C225" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G225">
         <v>1</v>
@@ -5433,100 +5955,100 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>78</v>
       </c>
       <c r="C226" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="M226">
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>78</v>
       </c>
       <c r="C227" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="H227">
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:13">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>78</v>
       </c>
       <c r="C228" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H228">
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:13">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>78</v>
       </c>
       <c r="C229" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="H229">
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:13">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>78</v>
       </c>
       <c r="C230" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="H230">
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:13">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>78</v>
       </c>
       <c r="C231" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="H231">
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:13">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>78</v>
       </c>
       <c r="C232" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="H232">
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:13">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>78</v>
       </c>
       <c r="C233" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G233">
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:13">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>81</v>
       </c>
       <c r="C234" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E234">
         <v>1</v>
@@ -5541,12 +6063,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:13">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>81</v>
       </c>
       <c r="C235" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E235">
         <v>1</v>
@@ -5561,12 +6083,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:13">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>81</v>
       </c>
       <c r="C236" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E236">
         <v>1</v>
@@ -5575,23 +6097,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:13">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
       <c r="C237" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E237">
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:13">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>81</v>
       </c>
       <c r="C238" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E238">
         <v>1</v>
@@ -5603,12 +6125,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>81</v>
       </c>
       <c r="C239" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -5617,12 +6139,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:13">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>81</v>
       </c>
       <c r="C240" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E240">
         <v>1</v>
@@ -5634,56 +6156,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:14">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>81</v>
       </c>
       <c r="C241" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E241">
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:14">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>81</v>
       </c>
       <c r="C242" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E242">
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:14">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>81</v>
       </c>
       <c r="C243" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E243">
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:14">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>81</v>
       </c>
       <c r="C244" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="E244">
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:14">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>81</v>
       </c>
       <c r="C245" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E245">
         <v>1</v>
@@ -5692,34 +6214,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:14">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>81</v>
       </c>
       <c r="C246" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="E246">
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:14">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>81</v>
       </c>
       <c r="C247" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G247">
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:14">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>81</v>
       </c>
       <c r="C248" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G248">
         <v>1</v>
@@ -5728,34 +6250,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:14">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>81</v>
       </c>
       <c r="C249" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E249">
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:14">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>81</v>
       </c>
       <c r="C250" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H250">
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:14">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>83</v>
       </c>
       <c r="C251" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D251">
         <v>1</v>
@@ -5770,12 +6292,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:14">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>83</v>
       </c>
       <c r="C252" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D252">
         <v>1</v>
@@ -5787,12 +6309,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:14">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>83</v>
       </c>
       <c r="C253" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -5801,12 +6323,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:14">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>83</v>
       </c>
       <c r="C254" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D254">
         <v>1</v>
@@ -5815,18 +6337,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:14">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>83</v>
       </c>
       <c r="C255" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="M255">
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:14">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>83</v>
       </c>
@@ -5834,13 +6356,13 @@
         <v>1</v>
       </c>
       <c r="C256" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="N256">
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:14">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>83</v>
       </c>
@@ -5848,13 +6370,13 @@
         <v>1</v>
       </c>
       <c r="C257" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="N257">
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:14">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>83</v>
       </c>
@@ -5862,13 +6384,13 @@
         <v>1</v>
       </c>
       <c r="C258" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="N258">
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:14">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>83</v>
       </c>
@@ -5876,13 +6398,13 @@
         <v>1</v>
       </c>
       <c r="C259" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="N259">
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:14">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>83</v>
       </c>
@@ -5890,13 +6412,13 @@
         <v>1</v>
       </c>
       <c r="C260" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="N260">
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:14">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>83</v>
       </c>
@@ -5904,13 +6426,13 @@
         <v>1</v>
       </c>
       <c r="C261" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="N261">
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:14">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>83</v>
       </c>
@@ -5918,18 +6440,18 @@
         <v>1</v>
       </c>
       <c r="C262" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="N262">
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:14">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>83</v>
       </c>
       <c r="C263" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G263">
         <v>1</v>
@@ -5938,34 +6460,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:14">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>83</v>
       </c>
       <c r="C264" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="M264">
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:14">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>83</v>
       </c>
       <c r="C265" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D265">
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:14">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>83</v>
       </c>
       <c r="C266" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D266">
         <v>1</v>
@@ -5974,86 +6496,86 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:14">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>83</v>
       </c>
       <c r="C267" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="268" spans="1:14">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>83</v>
       </c>
       <c r="C268" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D268">
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:14">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>83</v>
       </c>
       <c r="C269" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="D269">
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:14">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>83</v>
       </c>
       <c r="C270" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G270">
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:14">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>83</v>
       </c>
       <c r="C271" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E271">
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:14">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>83</v>
       </c>
       <c r="C272" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F272">
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:14">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>87</v>
       </c>
       <c r="C273" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G273">
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:14">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>87</v>
       </c>
       <c r="C274" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G274">
         <v>1</v>
@@ -6065,12 +6587,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:14">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>87</v>
       </c>
       <c r="C275" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G275">
         <v>1</v>
@@ -6082,34 +6604,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:14">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>87</v>
       </c>
       <c r="C276" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="H276">
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:14">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>87</v>
       </c>
       <c r="C277" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="H277">
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:14">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>87</v>
       </c>
       <c r="C278" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="H278">
         <v>1</v>
@@ -6118,12 +6640,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>87</v>
       </c>
       <c r="C279" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H279">
         <v>1</v>
@@ -6132,23 +6654,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>87</v>
       </c>
       <c r="C280" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H280">
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>87</v>
       </c>
       <c r="C281" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="H281">
         <v>1</v>
@@ -6157,12 +6679,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>87</v>
       </c>
       <c r="C282" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G282">
         <v>1</v>
@@ -6171,23 +6693,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>87</v>
       </c>
       <c r="C283" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="H283">
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>87</v>
       </c>
       <c r="C284" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G284">
         <v>1</v>
@@ -6196,89 +6718,89 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>87</v>
       </c>
       <c r="C285" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="H285">
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>87</v>
       </c>
       <c r="C286" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="N286">
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>87</v>
       </c>
       <c r="C287" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G287">
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>87</v>
       </c>
       <c r="C288" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="N288">
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:14">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>87</v>
       </c>
       <c r="C289" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="N289">
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:14">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>87</v>
       </c>
       <c r="C290" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="N290">
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:14">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>90</v>
       </c>
       <c r="C291" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H291">
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:14">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>90</v>
       </c>
       <c r="C292" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G292">
         <v>1</v>
@@ -6287,89 +6809,89 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:14">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>90</v>
       </c>
       <c r="C293" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H293">
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:14">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>90</v>
       </c>
       <c r="C294" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="H294">
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:14">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>90</v>
       </c>
       <c r="C295" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H295">
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:14">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>90</v>
       </c>
       <c r="C296" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="H296">
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:14">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>90</v>
       </c>
       <c r="C297" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="H297">
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:14">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>90</v>
       </c>
       <c r="C298" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G298">
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:14">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>90</v>
       </c>
       <c r="C299" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="H299">
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:14">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>93</v>
       </c>
       <c r="C300" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G300">
         <v>1</v>
@@ -6378,12 +6900,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:14">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>93</v>
       </c>
       <c r="C301" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G301">
         <v>1</v>
@@ -6392,12 +6914,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:14">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>93</v>
       </c>
       <c r="C302" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G302">
         <v>1</v>
@@ -6406,56 +6928,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:14">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>93</v>
       </c>
       <c r="C303" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G303">
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:14">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>93</v>
       </c>
       <c r="C304" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G304">
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>93</v>
       </c>
       <c r="C305" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="G305">
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>93</v>
       </c>
       <c r="C306" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H306">
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>93</v>
       </c>
       <c r="C307" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G307">
         <v>1</v>
@@ -6464,23 +6986,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>93</v>
       </c>
       <c r="C308" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="H308">
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="C309" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E309">
         <v>1</v>
@@ -6495,23 +7017,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="C310" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G310">
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="C311" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G311">
         <v>1</v>
@@ -6520,286 +7042,1847 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="C312" t="s">
+        <v>131</v>
+      </c>
+      <c r="G312">
+        <v>1</v>
+      </c>
+      <c r="K312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>306</v>
+      </c>
+      <c r="C313" t="s">
+        <v>186</v>
+      </c>
+      <c r="E313">
+        <v>1</v>
+      </c>
+      <c r="G313">
+        <v>1</v>
+      </c>
+      <c r="K313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>306</v>
+      </c>
+      <c r="C314" t="s">
+        <v>151</v>
+      </c>
+      <c r="E314">
+        <v>1</v>
+      </c>
+      <c r="F314">
+        <v>1</v>
+      </c>
+      <c r="K314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>306</v>
+      </c>
+      <c r="C315" t="s">
+        <v>161</v>
+      </c>
+      <c r="E315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>306</v>
+      </c>
+      <c r="C316" t="s">
+        <v>160</v>
+      </c>
+      <c r="E316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>306</v>
+      </c>
+      <c r="C317" t="s">
+        <v>209</v>
+      </c>
+      <c r="E317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>306</v>
+      </c>
+      <c r="C318" t="s">
+        <v>158</v>
+      </c>
+      <c r="E318">
+        <v>1</v>
+      </c>
+      <c r="K318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>306</v>
+      </c>
+      <c r="C319" t="s">
+        <v>240</v>
+      </c>
+      <c r="E319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>306</v>
+      </c>
+      <c r="C320" t="s">
+        <v>241</v>
+      </c>
+      <c r="E320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>306</v>
+      </c>
+      <c r="C321" t="s">
+        <v>124</v>
+      </c>
+      <c r="G321">
+        <v>1</v>
+      </c>
+      <c r="K321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>306</v>
+      </c>
+      <c r="C322" t="s">
+        <v>141</v>
+      </c>
+      <c r="K322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>306</v>
+      </c>
+      <c r="C323" t="s">
+        <v>242</v>
+      </c>
+      <c r="K323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>306</v>
+      </c>
+      <c r="C324" t="s">
+        <v>146</v>
+      </c>
+      <c r="G324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>306</v>
+      </c>
+      <c r="C325" t="s">
+        <v>225</v>
+      </c>
+      <c r="K325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>306</v>
+      </c>
+      <c r="C326" t="s">
+        <v>243</v>
+      </c>
+      <c r="K326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>306</v>
+      </c>
+      <c r="C327" t="s">
+        <v>216</v>
+      </c>
+      <c r="K327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>306</v>
+      </c>
+      <c r="C328" t="s">
+        <v>187</v>
+      </c>
+      <c r="K328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>306</v>
+      </c>
+      <c r="C329" t="s">
+        <v>238</v>
+      </c>
+      <c r="K329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>306</v>
+      </c>
+      <c r="C330" t="s">
+        <v>244</v>
+      </c>
+      <c r="K330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>306</v>
+      </c>
+      <c r="C331" t="s">
+        <v>245</v>
+      </c>
+      <c r="K331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>306</v>
+      </c>
+      <c r="B332" t="s">
+        <v>122</v>
+      </c>
+      <c r="C332" t="s">
+        <v>246</v>
+      </c>
+      <c r="K332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>306</v>
+      </c>
+      <c r="B333">
+        <v>1</v>
+      </c>
+      <c r="C333" t="s">
+        <v>247</v>
+      </c>
+      <c r="K333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>306</v>
+      </c>
+      <c r="B334">
+        <v>1</v>
+      </c>
+      <c r="C334" t="s">
+        <v>248</v>
+      </c>
+      <c r="K334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>97</v>
+      </c>
+      <c r="C335" t="s">
         <v>121</v>
       </c>
-      <c r="G312">
-        <v>1</v>
-      </c>
-      <c r="K312">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="313" spans="1:11">
-      <c r="A313" t="s">
-        <v>95</v>
-      </c>
-      <c r="C313" t="s">
-        <v>176</v>
-      </c>
-      <c r="E313">
-        <v>1</v>
-      </c>
-      <c r="G313">
-        <v>1</v>
-      </c>
-      <c r="K313">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="314" spans="1:11">
-      <c r="A314" t="s">
-        <v>95</v>
-      </c>
-      <c r="C314" t="s">
-        <v>141</v>
-      </c>
-      <c r="E314">
-        <v>1</v>
-      </c>
-      <c r="F314">
-        <v>1</v>
-      </c>
-      <c r="K314">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="315" spans="1:11">
-      <c r="A315" t="s">
-        <v>95</v>
-      </c>
-      <c r="C315" t="s">
+      <c r="G335">
+        <v>1</v>
+      </c>
+      <c r="K335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>97</v>
+      </c>
+      <c r="C336" t="s">
+        <v>146</v>
+      </c>
+      <c r="G336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>97</v>
+      </c>
+      <c r="C337" t="s">
+        <v>124</v>
+      </c>
+      <c r="E337">
+        <v>1</v>
+      </c>
+      <c r="G337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>97</v>
+      </c>
+      <c r="C338" t="s">
+        <v>169</v>
+      </c>
+      <c r="K338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>97</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>97</v>
+      </c>
+      <c r="B340">
+        <v>1</v>
+      </c>
+      <c r="C340" t="s">
+        <v>250</v>
+      </c>
+      <c r="K340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>97</v>
+      </c>
+      <c r="B341">
+        <v>1</v>
+      </c>
+      <c r="C341" t="s">
+        <v>251</v>
+      </c>
+      <c r="K341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>97</v>
+      </c>
+      <c r="B342">
+        <v>1</v>
+      </c>
+      <c r="C342" t="s">
+        <v>252</v>
+      </c>
+      <c r="K342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>97</v>
+      </c>
+      <c r="B343">
+        <v>1</v>
+      </c>
+      <c r="C343" t="s">
+        <v>253</v>
+      </c>
+      <c r="K343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>97</v>
+      </c>
+      <c r="B344">
+        <v>1</v>
+      </c>
+      <c r="C344" t="s">
+        <v>254</v>
+      </c>
+      <c r="K344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>97</v>
+      </c>
+      <c r="B345">
+        <v>1</v>
+      </c>
+      <c r="C345" t="s">
+        <v>255</v>
+      </c>
+      <c r="K345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>97</v>
+      </c>
+      <c r="B346">
+        <v>1</v>
+      </c>
+      <c r="C346" t="s">
+        <v>256</v>
+      </c>
+      <c r="K346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>97</v>
+      </c>
+      <c r="B347">
+        <v>1</v>
+      </c>
+      <c r="C347" t="s">
+        <v>257</v>
+      </c>
+      <c r="K347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>97</v>
+      </c>
+      <c r="C348" t="s">
+        <v>199</v>
+      </c>
+      <c r="E348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>97</v>
+      </c>
+      <c r="B349">
+        <v>1</v>
+      </c>
+      <c r="C349" t="s">
+        <v>258</v>
+      </c>
+      <c r="K349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>97</v>
+      </c>
+      <c r="B350">
+        <v>1</v>
+      </c>
+      <c r="C350" t="s">
+        <v>259</v>
+      </c>
+      <c r="K350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>97</v>
+      </c>
+      <c r="B351">
+        <v>1</v>
+      </c>
+      <c r="C351" t="s">
+        <v>260</v>
+      </c>
+      <c r="K351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>97</v>
+      </c>
+      <c r="B352">
+        <v>1</v>
+      </c>
+      <c r="C352" t="s">
+        <v>261</v>
+      </c>
+      <c r="K352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>97</v>
+      </c>
+      <c r="B353">
+        <v>1</v>
+      </c>
+      <c r="C353" t="s">
+        <v>262</v>
+      </c>
+      <c r="K353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>97</v>
+      </c>
+      <c r="B354">
+        <v>1</v>
+      </c>
+      <c r="C354" t="s">
+        <v>263</v>
+      </c>
+      <c r="K354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>97</v>
+      </c>
+      <c r="B355">
+        <v>1</v>
+      </c>
+      <c r="C355" t="s">
+        <v>264</v>
+      </c>
+      <c r="K355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>97</v>
+      </c>
+      <c r="B356">
+        <v>1</v>
+      </c>
+      <c r="C356" t="s">
+        <v>171</v>
+      </c>
+      <c r="K356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>97</v>
+      </c>
+      <c r="B357">
+        <v>1</v>
+      </c>
+      <c r="C357" t="s">
+        <v>265</v>
+      </c>
+      <c r="K357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>97</v>
+      </c>
+      <c r="B358">
+        <v>1</v>
+      </c>
+      <c r="C358" t="s">
+        <v>266</v>
+      </c>
+      <c r="K358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>99</v>
+      </c>
+      <c r="C359" t="s">
+        <v>158</v>
+      </c>
+      <c r="G359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>99</v>
+      </c>
+      <c r="C360" t="s">
+        <v>121</v>
+      </c>
+      <c r="G360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>99</v>
+      </c>
+      <c r="C361" t="s">
+        <v>129</v>
+      </c>
+      <c r="G361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>101</v>
+      </c>
+      <c r="C362" t="s">
+        <v>124</v>
+      </c>
+      <c r="D362">
+        <v>1</v>
+      </c>
+      <c r="E362">
+        <v>1</v>
+      </c>
+      <c r="G362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>101</v>
+      </c>
+      <c r="C363" t="s">
+        <v>163</v>
+      </c>
+      <c r="G363">
+        <v>1</v>
+      </c>
+      <c r="L363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>101</v>
+      </c>
+      <c r="C364" t="s">
         <v>151</v>
       </c>
-      <c r="E315">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="316" spans="1:11">
-      <c r="A316" t="s">
-        <v>95</v>
-      </c>
-      <c r="C316" t="s">
-        <v>150</v>
-      </c>
-      <c r="E316">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="317" spans="1:11">
-      <c r="A317" t="s">
-        <v>95</v>
-      </c>
-      <c r="C317" t="s">
-        <v>199</v>
-      </c>
-      <c r="E317">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="318" spans="1:11">
-      <c r="A318" t="s">
-        <v>95</v>
-      </c>
-      <c r="C318" t="s">
-        <v>148</v>
-      </c>
-      <c r="E318">
-        <v>1</v>
-      </c>
-      <c r="K318">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="319" spans="1:11">
-      <c r="A319" t="s">
-        <v>95</v>
-      </c>
-      <c r="C319" t="s">
-        <v>230</v>
-      </c>
-      <c r="E319">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="320" spans="1:11">
-      <c r="A320" t="s">
-        <v>95</v>
-      </c>
-      <c r="C320" t="s">
-        <v>231</v>
-      </c>
-      <c r="E320">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="321" spans="1:11">
-      <c r="A321" t="s">
-        <v>95</v>
-      </c>
-      <c r="C321" t="s">
-        <v>114</v>
-      </c>
-      <c r="G321">
-        <v>1</v>
-      </c>
-      <c r="K321">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="322" spans="1:11">
-      <c r="A322" t="s">
-        <v>95</v>
-      </c>
-      <c r="C322" t="s">
+      <c r="E364">
+        <v>1</v>
+      </c>
+      <c r="L364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>101</v>
+      </c>
+      <c r="C365" t="s">
+        <v>121</v>
+      </c>
+      <c r="G365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>101</v>
+      </c>
+      <c r="C366" t="s">
+        <v>249</v>
+      </c>
+      <c r="E366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>101</v>
+      </c>
+      <c r="C367" t="s">
+        <v>267</v>
+      </c>
+      <c r="E367">
+        <v>1</v>
+      </c>
+      <c r="L367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>101</v>
+      </c>
+      <c r="B368">
+        <v>1</v>
+      </c>
+      <c r="C368" t="s">
+        <v>268</v>
+      </c>
+      <c r="L368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>101</v>
+      </c>
+      <c r="C369" t="s">
+        <v>158</v>
+      </c>
+      <c r="L369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>101</v>
+      </c>
+      <c r="B370">
+        <v>1</v>
+      </c>
+      <c r="C370" t="s">
+        <v>269</v>
+      </c>
+      <c r="L370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>101</v>
+      </c>
+      <c r="B371">
+        <v>1</v>
+      </c>
+      <c r="C371" t="s">
+        <v>270</v>
+      </c>
+      <c r="L371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>101</v>
+      </c>
+      <c r="B372">
+        <v>1</v>
+      </c>
+      <c r="C372" t="s">
+        <v>271</v>
+      </c>
+      <c r="L372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>101</v>
+      </c>
+      <c r="C373" t="s">
+        <v>272</v>
+      </c>
+      <c r="L373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>101</v>
+      </c>
+      <c r="B374">
+        <v>1</v>
+      </c>
+      <c r="C374" t="s">
+        <v>273</v>
+      </c>
+      <c r="L374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>101</v>
+      </c>
+      <c r="B375">
+        <v>1</v>
+      </c>
+      <c r="C375" t="s">
+        <v>274</v>
+      </c>
+      <c r="L375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>101</v>
+      </c>
+      <c r="B376">
+        <v>1</v>
+      </c>
+      <c r="C376" t="s">
+        <v>275</v>
+      </c>
+      <c r="L376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>101</v>
+      </c>
+      <c r="B377">
+        <v>1</v>
+      </c>
+      <c r="C377" t="s">
+        <v>276</v>
+      </c>
+      <c r="L377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>101</v>
+      </c>
+      <c r="B378">
+        <v>1</v>
+      </c>
+      <c r="C378" t="s">
+        <v>277</v>
+      </c>
+      <c r="L378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>101</v>
+      </c>
+      <c r="B379">
+        <v>1</v>
+      </c>
+      <c r="C379" t="s">
+        <v>278</v>
+      </c>
+      <c r="L379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>101</v>
+      </c>
+      <c r="B380">
+        <v>1</v>
+      </c>
+      <c r="C380" t="s">
+        <v>279</v>
+      </c>
+      <c r="L380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>103</v>
+      </c>
+      <c r="C381" t="s">
+        <v>124</v>
+      </c>
+      <c r="E381">
+        <v>1</v>
+      </c>
+      <c r="G381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>103</v>
+      </c>
+      <c r="C382" t="s">
+        <v>121</v>
+      </c>
+      <c r="G382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>103</v>
+      </c>
+      <c r="C383" t="s">
+        <v>158</v>
+      </c>
+      <c r="G383">
+        <v>1</v>
+      </c>
+      <c r="K383">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>103</v>
+      </c>
+      <c r="C384" t="s">
+        <v>185</v>
+      </c>
+      <c r="E384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>103</v>
+      </c>
+      <c r="C385" t="s">
+        <v>215</v>
+      </c>
+      <c r="E385">
+        <v>1</v>
+      </c>
+      <c r="K385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>103</v>
+      </c>
+      <c r="B386">
+        <v>1</v>
+      </c>
+      <c r="C386" t="s">
+        <v>280</v>
+      </c>
+      <c r="K386">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>103</v>
+      </c>
+      <c r="B387">
+        <v>1</v>
+      </c>
+      <c r="C387" t="s">
+        <v>281</v>
+      </c>
+      <c r="K387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>103</v>
+      </c>
+      <c r="B388">
+        <v>1</v>
+      </c>
+      <c r="C388" t="s">
+        <v>282</v>
+      </c>
+      <c r="K388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>103</v>
+      </c>
+      <c r="B389">
+        <v>1</v>
+      </c>
+      <c r="C389" t="s">
+        <v>283</v>
+      </c>
+      <c r="K389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>103</v>
+      </c>
+      <c r="B390">
+        <v>1</v>
+      </c>
+      <c r="C390" t="s">
+        <v>284</v>
+      </c>
+      <c r="K390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>103</v>
+      </c>
+      <c r="B391">
+        <v>1</v>
+      </c>
+      <c r="C391" t="s">
+        <v>285</v>
+      </c>
+      <c r="K391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>103</v>
+      </c>
+      <c r="B392">
+        <v>1</v>
+      </c>
+      <c r="C392" t="s">
+        <v>286</v>
+      </c>
+      <c r="K392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>103</v>
+      </c>
+      <c r="B393">
+        <v>1</v>
+      </c>
+      <c r="C393" t="s">
+        <v>287</v>
+      </c>
+      <c r="K393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>103</v>
+      </c>
+      <c r="B394">
+        <v>1</v>
+      </c>
+      <c r="C394" t="s">
+        <v>288</v>
+      </c>
+      <c r="K394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>103</v>
+      </c>
+      <c r="B395">
+        <v>1</v>
+      </c>
+      <c r="C395" t="s">
+        <v>289</v>
+      </c>
+      <c r="K395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>103</v>
+      </c>
+      <c r="B396">
+        <v>1</v>
+      </c>
+      <c r="C396" t="s">
+        <v>290</v>
+      </c>
+      <c r="K396">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>103</v>
+      </c>
+      <c r="B397">
+        <v>1</v>
+      </c>
+      <c r="C397" t="s">
+        <v>291</v>
+      </c>
+      <c r="K397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>103</v>
+      </c>
+      <c r="B398">
+        <v>1</v>
+      </c>
+      <c r="C398" t="s">
+        <v>292</v>
+      </c>
+      <c r="K398">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>103</v>
+      </c>
+      <c r="B399">
+        <v>1</v>
+      </c>
+      <c r="C399" t="s">
+        <v>293</v>
+      </c>
+      <c r="K399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>103</v>
+      </c>
+      <c r="B400">
+        <v>1</v>
+      </c>
+      <c r="C400" t="s">
+        <v>294</v>
+      </c>
+      <c r="K400">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>103</v>
+      </c>
+      <c r="B401">
+        <v>1</v>
+      </c>
+      <c r="C401" t="s">
+        <v>295</v>
+      </c>
+      <c r="K401">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>103</v>
+      </c>
+      <c r="B402">
+        <v>1</v>
+      </c>
+      <c r="C402" t="s">
+        <v>296</v>
+      </c>
+      <c r="K402">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>103</v>
+      </c>
+      <c r="C403" t="s">
+        <v>297</v>
+      </c>
+      <c r="K403">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>103</v>
+      </c>
+      <c r="B404">
+        <v>1</v>
+      </c>
+      <c r="C404" t="s">
+        <v>119</v>
+      </c>
+      <c r="K404">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>103</v>
+      </c>
+      <c r="C405" t="s">
+        <v>298</v>
+      </c>
+      <c r="K405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>103</v>
+      </c>
+      <c r="C406" t="s">
+        <v>118</v>
+      </c>
+      <c r="K406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>103</v>
+      </c>
+      <c r="C407" t="s">
         <v>131</v>
       </c>
-      <c r="K322">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="323" spans="1:11">
-      <c r="A323" t="s">
-        <v>95</v>
-      </c>
-      <c r="C323" t="s">
-        <v>232</v>
-      </c>
-      <c r="K323">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="324" spans="1:11">
-      <c r="A324" t="s">
-        <v>95</v>
-      </c>
-      <c r="C324" t="s">
-        <v>136</v>
-      </c>
-      <c r="G324">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="325" spans="1:11">
-      <c r="A325" t="s">
-        <v>95</v>
-      </c>
-      <c r="C325" t="s">
-        <v>215</v>
-      </c>
-      <c r="K325">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="326" spans="1:11">
-      <c r="A326" t="s">
-        <v>95</v>
-      </c>
-      <c r="C326" t="s">
-        <v>233</v>
-      </c>
-      <c r="K326">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="327" spans="1:11">
-      <c r="A327" t="s">
-        <v>95</v>
-      </c>
-      <c r="C327" t="s">
-        <v>206</v>
-      </c>
-      <c r="K327">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="328" spans="1:11">
-      <c r="A328" t="s">
-        <v>95</v>
-      </c>
-      <c r="C328" t="s">
-        <v>177</v>
-      </c>
-      <c r="K328">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="329" spans="1:11">
-      <c r="A329" t="s">
-        <v>95</v>
-      </c>
-      <c r="C329" t="s">
-        <v>228</v>
-      </c>
-      <c r="K329">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="330" spans="1:11">
-      <c r="A330" t="s">
-        <v>95</v>
-      </c>
-      <c r="C330" t="s">
-        <v>234</v>
-      </c>
-      <c r="K330">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="331" spans="1:11">
-      <c r="A331" t="s">
-        <v>95</v>
-      </c>
-      <c r="C331" t="s">
-        <v>235</v>
-      </c>
-      <c r="K331">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="332" spans="1:11">
-      <c r="A332" t="s">
-        <v>95</v>
-      </c>
-      <c r="B332" t="s">
-        <v>112</v>
-      </c>
-      <c r="C332" t="s">
-        <v>236</v>
-      </c>
-      <c r="K332">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="333" spans="1:11">
-      <c r="A333" t="s">
-        <v>95</v>
-      </c>
-      <c r="B333">
-        <v>1</v>
-      </c>
-      <c r="C333" t="s">
-        <v>237</v>
-      </c>
-      <c r="K333">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="334" spans="1:11">
-      <c r="A334" t="s">
-        <v>95</v>
-      </c>
-      <c r="B334">
-        <v>1</v>
-      </c>
-      <c r="C334" t="s">
-        <v>238</v>
-      </c>
-      <c r="K334">
+      <c r="K407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>103</v>
+      </c>
+      <c r="C408" t="s">
+        <v>299</v>
+      </c>
+      <c r="K408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>103</v>
+      </c>
+      <c r="C409" t="s">
+        <v>167</v>
+      </c>
+      <c r="K409">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>103</v>
+      </c>
+      <c r="C410" t="s">
+        <v>157</v>
+      </c>
+      <c r="K410">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>104</v>
+      </c>
+      <c r="C411" t="s">
+        <v>160</v>
+      </c>
+      <c r="E411">
+        <v>1</v>
+      </c>
+      <c r="G411">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>104</v>
+      </c>
+      <c r="C412" t="s">
+        <v>300</v>
+      </c>
+      <c r="E412">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>104</v>
+      </c>
+      <c r="C413" t="s">
+        <v>163</v>
+      </c>
+      <c r="D413">
+        <v>1</v>
+      </c>
+      <c r="E413">
+        <v>1</v>
+      </c>
+      <c r="G413">
+        <v>1</v>
+      </c>
+      <c r="K413">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>104</v>
+      </c>
+      <c r="C414" t="s">
+        <v>158</v>
+      </c>
+      <c r="E414">
+        <v>1</v>
+      </c>
+      <c r="G414">
+        <v>1</v>
+      </c>
+      <c r="K414">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>104</v>
+      </c>
+      <c r="C415" t="s">
+        <v>121</v>
+      </c>
+      <c r="D415">
+        <v>1</v>
+      </c>
+      <c r="E415">
+        <v>1</v>
+      </c>
+      <c r="G415">
+        <v>1</v>
+      </c>
+      <c r="K415">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>104</v>
+      </c>
+      <c r="C416" t="s">
+        <v>124</v>
+      </c>
+      <c r="D416">
+        <v>1</v>
+      </c>
+      <c r="E416">
+        <v>1</v>
+      </c>
+      <c r="G416">
+        <v>1</v>
+      </c>
+      <c r="K416">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>104</v>
+      </c>
+      <c r="C417" t="s">
+        <v>157</v>
+      </c>
+      <c r="D417">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>104</v>
+      </c>
+      <c r="C418" t="s">
+        <v>131</v>
+      </c>
+      <c r="D418">
+        <v>1</v>
+      </c>
+      <c r="G418">
+        <v>1</v>
+      </c>
+      <c r="K418">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>104</v>
+      </c>
+      <c r="C419" t="s">
+        <v>209</v>
+      </c>
+      <c r="G419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>104</v>
+      </c>
+      <c r="B420">
+        <v>1</v>
+      </c>
+      <c r="C420" t="s">
+        <v>280</v>
+      </c>
+      <c r="K420">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>104</v>
+      </c>
+      <c r="B421">
+        <v>1</v>
+      </c>
+      <c r="C421" t="s">
+        <v>281</v>
+      </c>
+      <c r="K421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>104</v>
+      </c>
+      <c r="B422">
+        <v>1</v>
+      </c>
+      <c r="C422" t="s">
+        <v>282</v>
+      </c>
+      <c r="K422">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>104</v>
+      </c>
+      <c r="B423">
+        <v>1</v>
+      </c>
+      <c r="C423" t="s">
+        <v>283</v>
+      </c>
+      <c r="K423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>104</v>
+      </c>
+      <c r="B424">
+        <v>1</v>
+      </c>
+      <c r="C424" t="s">
+        <v>284</v>
+      </c>
+      <c r="K424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>104</v>
+      </c>
+      <c r="B425">
+        <v>1</v>
+      </c>
+      <c r="C425" t="s">
+        <v>285</v>
+      </c>
+      <c r="K425">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>104</v>
+      </c>
+      <c r="B426">
+        <v>1</v>
+      </c>
+      <c r="C426" t="s">
+        <v>286</v>
+      </c>
+      <c r="K426">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>104</v>
+      </c>
+      <c r="B427">
+        <v>1</v>
+      </c>
+      <c r="C427" t="s">
+        <v>287</v>
+      </c>
+      <c r="K427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>104</v>
+      </c>
+      <c r="B428">
+        <v>1</v>
+      </c>
+      <c r="C428" t="s">
+        <v>288</v>
+      </c>
+      <c r="K428">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>104</v>
+      </c>
+      <c r="B429">
+        <v>1</v>
+      </c>
+      <c r="C429" t="s">
+        <v>289</v>
+      </c>
+      <c r="K429">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>104</v>
+      </c>
+      <c r="B430">
+        <v>1</v>
+      </c>
+      <c r="C430" t="s">
+        <v>290</v>
+      </c>
+      <c r="K430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>104</v>
+      </c>
+      <c r="B431">
+        <v>1</v>
+      </c>
+      <c r="C431" t="s">
+        <v>291</v>
+      </c>
+      <c r="K431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>104</v>
+      </c>
+      <c r="B432">
+        <v>1</v>
+      </c>
+      <c r="C432" t="s">
+        <v>292</v>
+      </c>
+      <c r="K432">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>104</v>
+      </c>
+      <c r="B433">
+        <v>1</v>
+      </c>
+      <c r="C433" t="s">
+        <v>293</v>
+      </c>
+      <c r="K433">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>104</v>
+      </c>
+      <c r="B434">
+        <v>1</v>
+      </c>
+      <c r="C434" t="s">
+        <v>294</v>
+      </c>
+      <c r="K434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>104</v>
+      </c>
+      <c r="B435">
+        <v>1</v>
+      </c>
+      <c r="C435" t="s">
+        <v>295</v>
+      </c>
+      <c r="K435">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>104</v>
+      </c>
+      <c r="B436">
+        <v>1</v>
+      </c>
+      <c r="C436" t="s">
+        <v>296</v>
+      </c>
+      <c r="K436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>104</v>
+      </c>
+      <c r="B437">
+        <v>1</v>
+      </c>
+      <c r="C437" t="s">
+        <v>301</v>
+      </c>
+      <c r="K437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>104</v>
+      </c>
+      <c r="B438">
+        <v>1</v>
+      </c>
+      <c r="C438" t="s">
+        <v>302</v>
+      </c>
+      <c r="K438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>104</v>
+      </c>
+      <c r="B439">
+        <v>1</v>
+      </c>
+      <c r="C439" t="s">
+        <v>303</v>
+      </c>
+      <c r="K439">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>104</v>
+      </c>
+      <c r="B440">
+        <v>1</v>
+      </c>
+      <c r="C440" t="s">
+        <v>304</v>
+      </c>
+      <c r="K440">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>104</v>
+      </c>
+      <c r="B441">
+        <v>1</v>
+      </c>
+      <c r="C441" t="s">
+        <v>170</v>
+      </c>
+      <c r="K441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>104</v>
+      </c>
+      <c r="C442" t="s">
+        <v>297</v>
+      </c>
+      <c r="K442">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>104</v>
+      </c>
+      <c r="C443" t="s">
+        <v>194</v>
+      </c>
+      <c r="K443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>104</v>
+      </c>
+      <c r="C444" t="s">
+        <v>305</v>
+      </c>
+      <c r="G444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>104</v>
+      </c>
+      <c r="C445" t="s">
+        <v>219</v>
+      </c>
+      <c r="K445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>106</v>
+      </c>
+      <c r="C446" t="s">
+        <v>121</v>
+      </c>
+      <c r="E446">
+        <v>1</v>
+      </c>
+      <c r="G446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>106</v>
+      </c>
+      <c r="C447" t="s">
+        <v>163</v>
+      </c>
+      <c r="E447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>106</v>
+      </c>
+      <c r="C448" t="s">
+        <v>158</v>
+      </c>
+      <c r="E448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>106</v>
+      </c>
+      <c r="C449" t="s">
+        <v>124</v>
+      </c>
+      <c r="E449">
+        <v>1</v>
+      </c>
+      <c r="G449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>106</v>
+      </c>
+      <c r="C450" t="s">
+        <v>146</v>
+      </c>
+      <c r="G450">
         <v>1</v>
       </c>
     </row>
@@ -6809,6 +8892,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0278717-252d-455f-9297-341259384352">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="67fd2e6b-9b4b-488b-ae5d-884371a2c380" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F98E057C991C64EA8C44B2688F4F4E8" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="205ac32a36de600e2ab9bca4f1502e82">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0278717-252d-455f-9297-341259384352" xmlns:ns3="67fd2e6b-9b4b-488b-ae5d-884371a2c380" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="423e538afa53ae88b73bb7a22e6ab62a" ns2:_="" ns3:_="">
     <xsd:import namespace="b0278717-252d-455f-9297-341259384352"/>
@@ -6997,7 +9091,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -7006,25 +9100,40 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0278717-252d-455f-9297-341259384352">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="67fd2e6b-9b4b-488b-ae5d-884371a2c380" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75991279-CDFD-432A-85F7-9F9EBD8C5574}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87681022-589A-4D48-98F7-B0B4DE2A50CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b0278717-252d-455f-9297-341259384352"/>
+    <ds:schemaRef ds:uri="67fd2e6b-9b4b-488b-ae5d-884371a2c380"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5032AD0-6421-44B7-9938-A4A0BC003650}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75991279-CDFD-432A-85F7-9F9EBD8C5574}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b0278717-252d-455f-9297-341259384352"/>
+    <ds:schemaRef ds:uri="67fd2e6b-9b4b-488b-ae5d-884371a2c380"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87681022-589A-4D48-98F7-B0B4DE2A50CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5032AD0-6421-44B7-9938-A4A0BC003650}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>